--- a/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,388 +656,400 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1537000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1554000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1602000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1549000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1560000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1618000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1686000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1506000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1454000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1496000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1477000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1419000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1501000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1362000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1029000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1179000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1304000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1226000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1242000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1216000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1266000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1200000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1196000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1165000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1209000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1152000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1096000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1062000</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1114000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1137000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1166000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1129000</v>
       </c>
       <c r="G9" s="3">
         <v>1129000</v>
       </c>
       <c r="H9" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1188000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1219000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1072000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1058000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1080000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1096000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1051000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1076000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>990000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>789000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>892000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>930000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>932000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>933000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>903000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>936000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>853000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>850000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>822000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>848000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>816000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>788000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>751000</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>423000</v>
+      </c>
+      <c r="E10" s="3">
         <v>417000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>436000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>420000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>431000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>430000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>467000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>434000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>396000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>416000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>381000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>368000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>425000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>372000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>240000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>287000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>374000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>294000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>309000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>313000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>330000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>347000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>346000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>343000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>361000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>336000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>308000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>311000</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1068,44 +1080,45 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E12" s="3">
         <v>28000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>29000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>28000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22000</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1154,8 +1167,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1240,76 +1256,79 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E14" s="3">
         <v>81000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>46000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>43000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>76000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>43000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>45000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>41000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>35000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>57000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>36000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>59000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-17000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>40000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1326,32 +1345,35 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E15" s="3">
         <v>9000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>10000</v>
       </c>
       <c r="H15" s="3">
         <v>10000</v>
       </c>
       <c r="I15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J15" s="3">
         <v>9000</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1367,8 +1389,8 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1412,8 +1434,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1441,180 +1466,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1440000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1488000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1493000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1452000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1503000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1506000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1545000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1375000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1348000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1386000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1392000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1348000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1349000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1231000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1035000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1145000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1232000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1167000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1200000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1131000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1208000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1218000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1190000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1188000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1095000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1057000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1015000</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E18" s="3">
         <v>66000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>109000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>97000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>57000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>112000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>141000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>131000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>106000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>110000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>85000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>71000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>152000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>131000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>34000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>72000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>59000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>42000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>85000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>58000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>78000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>21000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>57000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>39000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1645,79 +1677,80 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-13000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2000</v>
       </c>
       <c r="F20" s="3">
         <v>2000</v>
       </c>
       <c r="G20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="3">
         <v>31000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>15000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-41000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-29000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-42000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-64000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-35000</v>
       </c>
       <c r="U20" s="3">
         <v>-35000</v>
       </c>
       <c r="V20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="W20" s="3">
         <v>16000</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>1000</v>
       </c>
       <c r="AA20" s="3">
         <v>1000</v>
@@ -1726,165 +1759,171 @@
         <v>1000</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E21" s="3">
         <v>75000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>136000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>123000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>113000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>135000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>170000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>152000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>134000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>131000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>115000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>109000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>133000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>118000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-14000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>33000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>43000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>27000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>117000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>75000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>21000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>96000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>39000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>75000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>56000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="3">
         <v>16000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>18000</v>
       </c>
       <c r="G22" s="3">
         <v>18000</v>
       </c>
       <c r="H22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="I22" s="3">
         <v>15000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>11000</v>
       </c>
       <c r="K22" s="3">
         <v>11000</v>
       </c>
       <c r="L22" s="3">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="M22" s="3">
         <v>12000</v>
       </c>
       <c r="N22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="O22" s="3">
         <v>13000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>14000</v>
       </c>
       <c r="P22" s="3">
         <v>14000</v>
       </c>
       <c r="Q22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="R22" s="3">
         <v>18000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>17000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>16000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>17000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20000</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1903,180 +1942,189 @@
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E23" s="3">
         <v>37000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>94000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>81000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>70000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>96000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>131000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>121000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>102000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>97000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>81000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>73000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>97000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>82000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-53000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-25000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>84000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>38000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>79000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>22000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>58000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>39000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E24" s="3">
         <v>16000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>44000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>24000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>31000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>33000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>37000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>34000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>35000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>29000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>24000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>38000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>23000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1000</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>36000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>339100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-329000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>34000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>18000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>35000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>23000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2161,180 +2209,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E26" s="3">
         <v>21000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>50000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>57000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>39000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>63000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>94000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>87000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>67000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>68000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>58000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>59000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>75000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-76000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>48000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-301100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>311000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>30000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>45000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>23000</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>16000</v>
       </c>
       <c r="AD26" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E27" s="3">
         <v>21000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>50000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>57000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>39000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>63000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>94000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>87000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>67000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>68000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>58000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>49000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>59000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>75000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-76000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>48000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-301100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>311000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>30000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>45000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>23000</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>16000</v>
       </c>
       <c r="AD27" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2419,8 +2476,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2463,8 +2523,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2481,32 +2541,35 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>317100</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>3000</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-453000</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2591,8 +2654,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2677,79 +2743,82 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E32" s="3">
         <v>13000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-2000</v>
       </c>
       <c r="F32" s="3">
         <v>-2000</v>
       </c>
       <c r="G32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-31000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-15000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>41000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>35000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>29000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>42000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>64000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>35000</v>
       </c>
       <c r="U32" s="3">
         <v>35000</v>
       </c>
       <c r="V32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="W32" s="3">
         <v>-16000</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA32" s="3">
         <v>-1000</v>
@@ -2758,99 +2827,105 @@
         <v>-1000</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E33" s="3">
         <v>21000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>50000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>57000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>39000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>63000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>94000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>87000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>67000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>68000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>58000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>49000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>59000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>75000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-76000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>48000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>16000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>311000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>33000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>45000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-449000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>23000</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>16000</v>
       </c>
       <c r="AD33" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2935,185 +3010,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E35" s="3">
         <v>21000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>50000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>57000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>39000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>63000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>94000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>87000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>67000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>68000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>58000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>49000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>59000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>75000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-76000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>48000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>16000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>311000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>33000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>45000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-449000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>23000</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>16000</v>
       </c>
       <c r="AD35" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3144,8 +3228,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3176,83 +3261,84 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>636000</v>
+      </c>
+      <c r="E41" s="3">
         <v>368000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>381000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>292000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>326000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>252000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>251000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>244000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>779000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>686000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>579000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>508000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>517000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>260000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>362000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>338000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>122000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>132000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>142000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>212000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>265000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>184000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>93000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>75000</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3262,8 +3348,11 @@
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3348,83 +3437,86 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>973000</v>
+      </c>
+      <c r="E43" s="3">
         <v>988000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1043000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>985000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1002000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1043000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1073000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1008000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>876000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>932000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>895000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>875000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>863000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>884000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>704000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>820000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>817000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>845000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>835000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>838000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>821000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>809000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>766000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>756000</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3434,83 +3526,86 @@
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>941000</v>
+      </c>
+      <c r="E44" s="3">
         <v>970000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1001000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1008000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>975000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>957000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>971000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>922000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>740000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>710000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>684000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>681000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>672000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>618000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>614000</v>
-      </c>
-      <c r="R44" s="3">
-        <v>671000</v>
       </c>
       <c r="S44" s="3">
         <v>671000</v>
       </c>
       <c r="T44" s="3">
+        <v>671000</v>
+      </c>
+      <c r="U44" s="3">
         <v>729000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>722000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>701000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>628000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>603000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>523000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>481000</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3520,83 +3615,86 @@
       <c r="AD44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E45" s="3">
         <v>289000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>197000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>210000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>199000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>198000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>186000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>165000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>146000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>179000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>198000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>156000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>173000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>161000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>163000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>164000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>175000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>134000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>147000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>111000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>95000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>72000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>74000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>65000</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3606,83 +3704,86 @@
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2743000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2615000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2622000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2495000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2502000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2450000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2481000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2339000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2541000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2507000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2356000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2220000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2225000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1923000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1843000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1993000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1785000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1840000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1846000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1862000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1809000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1668000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1456000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1377000</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3692,8 +3793,11 @@
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3778,83 +3882,86 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>582000</v>
+      </c>
+      <c r="E48" s="3">
         <v>577000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>580000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>571000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>557000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>538000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>535000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>514000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>428000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>424000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>438000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>442000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>451000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>445000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>440000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>433000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>453000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>436000</v>
       </c>
       <c r="U48" s="3">
         <v>436000</v>
       </c>
       <c r="V48" s="3">
+        <v>436000</v>
+      </c>
+      <c r="W48" s="3">
         <v>413000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>300000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>276000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>264000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>267000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3864,83 +3971,86 @@
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3166000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3143000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3204000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3207000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3199000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3138000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3158000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3125000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2661000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2671000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2682000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2675000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2691000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2657000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2638000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2612000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2769000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2757000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2777000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2772000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2767000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2776000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2766000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2810000</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3950,8 +4060,11 @@
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4036,8 +4149,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4122,83 +4238,86 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E52" s="3">
         <v>124000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>130000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>126000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>129000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>136000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>142000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>267000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>223000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>232000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>236000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>239000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>243000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>244000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>245000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>249000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>121000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>100000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>101000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>97000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>96000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>22000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>21000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>28000</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4208,8 +4327,11 @@
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4294,83 +4416,86 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6645000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6459000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6536000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6399000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6387000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6262000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6316000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6245000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5853000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5834000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5712000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5576000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5610000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5269000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5166000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5287000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5128000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5133000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5160000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5144000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4972000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4742000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4507000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4482000</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4380,8 +4505,11 @@
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4412,8 +4540,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4444,83 +4573,84 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>905000</v>
+      </c>
+      <c r="E57" s="3">
         <v>863000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>948000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>894000</v>
       </c>
       <c r="G57" s="3">
         <v>894000</v>
       </c>
       <c r="H57" s="3">
+        <v>894000</v>
+      </c>
+      <c r="I57" s="3">
         <v>936000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>987000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>958000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>883000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>905000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>915000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>908000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>936000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>858000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>811000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>906000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>920000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>932000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1009000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1013000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>964000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>850000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>774000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>712000</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4530,8 +4660,11 @@
       <c r="AD57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4557,7 +4690,7 @@
         <v>12000</v>
       </c>
       <c r="K58" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="L58" s="3">
         <v>10000</v>
@@ -4569,25 +4702,25 @@
         <v>10000</v>
       </c>
       <c r="O58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="P58" s="3">
         <v>7000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>181000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>287000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>382000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>22000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>88000</v>
-      </c>
-      <c r="U58" s="3">
-        <v>22000</v>
       </c>
       <c r="V58" s="3">
         <v>22000</v>
@@ -4595,8 +4728,8 @@
       <c r="W58" s="3">
         <v>22000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>8</v>
+      <c r="X58" s="3">
+        <v>22000</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>8</v>
@@ -4616,83 +4749,86 @@
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>608000</v>
+      </c>
+      <c r="E59" s="3">
         <v>592000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>564000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>563000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>640000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>594000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>580000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>576000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>601000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>617000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>586000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>528000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>595000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>606000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>564000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>467000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>552000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>531000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>528000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>524000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>503000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>550000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>459000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>418000</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4702,83 +4838,86 @@
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1525000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1467000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1524000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1469000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1546000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1542000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1579000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1546000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1494000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1532000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1511000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1446000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1538000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1645000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1662000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1755000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1494000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1551000</v>
-      </c>
-      <c r="U60" s="3">
-        <v>1559000</v>
       </c>
       <c r="V60" s="3">
         <v>1559000</v>
       </c>
       <c r="W60" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="X60" s="3">
         <v>1489000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1400000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1233000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1130000</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4788,74 +4927,77 @@
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1396000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1397000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1400000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1402000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1404000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1407000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1410000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1412000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1220000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1222000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1184000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1186000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1155000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1006000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1011000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1149000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1158000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1165000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1169000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1174000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1179000</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4874,83 +5016,86 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>975000</v>
+      </c>
+      <c r="E62" s="3">
         <v>950000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>935000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>924000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>908000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>913000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>933000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>926000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>887000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>922000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>914000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>912000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>924000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1013000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>998000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>862000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>874000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>844000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>839000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>819000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>771000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>657000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>794000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>763000</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4960,8 +5105,11 @@
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5046,8 +5194,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5132,8 +5283,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5218,83 +5372,86 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3896000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3814000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3859000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3795000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3858000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3862000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3922000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3884000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3601000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3676000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3609000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3544000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3617000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3664000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3671000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3766000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3526000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3560000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3567000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3552000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3439000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2057000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2027000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1893000</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5304,8 +5461,11 @@
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5336,8 +5496,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5422,8 +5583,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5508,8 +5672,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5594,8 +5761,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5680,74 +5850,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>810000</v>
+      </c>
+      <c r="E72" s="3">
         <v>728000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>707000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>657000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>600000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>561000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>498000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>404000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>317000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>250000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>182000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>124000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>75000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-59000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>38000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>47000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>39000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>50000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5766,8 +5939,11 @@
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5852,8 +6028,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5938,8 +6117,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6024,83 +6206,86 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2749000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2645000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2677000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2604000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2529000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2400000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2394000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2361000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2252000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2158000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2103000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2032000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1993000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1605000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1495000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1521000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1602000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1573000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1593000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1592000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1533000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2685000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2480000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2589000</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6110,8 +6295,11 @@
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6196,185 +6384,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E81" s="3">
         <v>21000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>50000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>57000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>39000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>63000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>94000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>87000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>67000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>68000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>58000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>49000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>59000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>75000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-76000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>48000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>16000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>311000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>33000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>45000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-449000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>23000</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>16000</v>
       </c>
       <c r="AD81" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6405,82 +6602,83 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E83" s="3">
         <v>22000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>22000</v>
       </c>
       <c r="M83" s="3">
         <v>22000</v>
       </c>
       <c r="N83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="O83" s="3">
         <v>23000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>22000</v>
       </c>
       <c r="P83" s="3">
         <v>22000</v>
       </c>
       <c r="Q83" s="3">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="R83" s="3">
         <v>21000</v>
       </c>
       <c r="S83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="T83" s="3">
         <v>25000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>19000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>16000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>16000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>13000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20000</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>17000</v>
       </c>
       <c r="AB83" s="3">
         <v>17000</v>
@@ -6489,10 +6687,13 @@
         <v>17000</v>
       </c>
       <c r="AD83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AE83" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6577,8 +6778,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6663,8 +6867,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6749,8 +6956,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6835,8 +7045,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6921,94 +7134,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E89" s="3">
         <v>60000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>121000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>139000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>37000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>35000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-59000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>112000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>104000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>94000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>152000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>145000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-74000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>93000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-33000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-27000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>87000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>117000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>132000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>126000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-143000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>111000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>30000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7039,94 +7258,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-29000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-51000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-29000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-28000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-23000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-40000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7211,8 +7434,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7297,94 +7523,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-57000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-37000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-665000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-18000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-24000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-18000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-51000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-29000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-28000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-34000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-21000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-18000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-39000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7415,8 +7647,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7501,8 +7734,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7587,8 +7823,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7673,8 +7912,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7759,262 +8001,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-29000</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-9000</v>
       </c>
       <c r="F100" s="3">
         <v>-9000</v>
       </c>
       <c r="G100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="H100" s="3">
         <v>-12000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>189000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>118000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-106000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-108000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>349000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-75000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>53000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-23000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>19000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>15000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-102000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>157000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-88000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-28000</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-13000</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>2000</v>
       </c>
       <c r="Q101" s="3">
         <v>2000</v>
       </c>
       <c r="R101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S101" s="3">
         <v>-8000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>2000</v>
       </c>
       <c r="AC101" s="3">
         <v>2000</v>
       </c>
       <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+        <v>2000</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>87000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-33000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>74000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>11000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-535000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>93000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>107000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>71000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>257000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-102000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>24000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>216000</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-10000</v>
       </c>
       <c r="T102" s="3">
         <v>-10000</v>
       </c>
       <c r="U102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="V102" s="3">
         <v>-70000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-53000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>81000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>91000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>19000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>10000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
@@ -656,400 +656,413 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1486000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1537000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1554000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1602000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1549000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1560000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1618000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1686000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1506000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1454000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1496000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1477000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1419000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1501000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1362000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1029000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1179000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1304000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1226000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1242000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1216000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1266000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1200000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1196000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1165000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1209000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1152000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1096000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1062000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1086000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1114000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1137000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1166000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1129000</v>
       </c>
       <c r="H9" s="3">
         <v>1129000</v>
       </c>
       <c r="I9" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="J9" s="3">
         <v>1188000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1219000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1072000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1058000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1080000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1096000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1051000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1076000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>990000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>789000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>892000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>930000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>932000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>933000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>903000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>936000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>853000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>850000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>822000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>848000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>816000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>788000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>751000</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>400000</v>
+      </c>
+      <c r="E10" s="3">
         <v>423000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>417000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>436000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>420000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>431000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>430000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>467000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>434000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>396000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>416000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>381000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>368000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>425000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>372000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>240000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>287000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>374000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>294000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>309000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>313000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>330000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>347000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>346000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>343000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>361000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>336000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>308000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>311000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1081,8 +1094,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,38 +1104,38 @@
         <v>25000</v>
       </c>
       <c r="E12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F12" s="3">
         <v>28000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>29000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>30000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>28000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22000</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1170,8 +1184,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1259,8 +1276,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1268,70 +1288,70 @@
         <v>50000</v>
       </c>
       <c r="E14" s="3">
+        <v>32000</v>
+      </c>
+      <c r="F14" s="3">
         <v>81000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>46000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>43000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>76000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>43000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>45000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>41000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>35000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>57000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>36000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>59000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-17000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>10000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>40000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1348,35 +1368,38 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E15" s="3">
         <v>10000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>10000</v>
       </c>
       <c r="I15" s="3">
         <v>10000</v>
       </c>
       <c r="J15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K15" s="3">
         <v>9000</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1392,8 +1415,8 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1437,8 +1460,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1467,186 +1493,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1440000</v>
+        <v>1401000</v>
       </c>
       <c r="E17" s="3">
+        <v>1422000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1488000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1493000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1452000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1503000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1506000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1545000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1375000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1348000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1386000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1392000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1348000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1349000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1231000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1035000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1145000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1232000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1167000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1200000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1131000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1208000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1218000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1190000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1188000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1095000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1057000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1015000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>115000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>66000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>109000</v>
+      </c>
+      <c r="H18" s="3">
         <v>97000</v>
       </c>
-      <c r="E18" s="3">
-        <v>66000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>109000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>97000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>57000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>112000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>141000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>131000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>106000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>110000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>85000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>71000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>152000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>131000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>34000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>72000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>59000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>42000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>85000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>58000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>78000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>21000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>57000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>39000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1678,82 +1711,83 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="E20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-13000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2000</v>
       </c>
       <c r="G20" s="3">
         <v>2000</v>
       </c>
       <c r="H20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I20" s="3">
         <v>31000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-35000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-29000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-42000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-64000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-35000</v>
       </c>
       <c r="V20" s="3">
         <v>-35000</v>
       </c>
       <c r="W20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="X20" s="3">
         <v>16000</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>1000</v>
       </c>
       <c r="AB20" s="3">
         <v>1000</v>
@@ -1762,171 +1796,177 @@
         <v>1000</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E21" s="3">
         <v>143000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>75000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>136000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>123000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>113000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>135000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>170000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>152000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>134000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>131000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>115000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>109000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>133000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>118000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-14000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>33000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>43000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>27000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>117000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>75000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>21000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>96000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>39000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>75000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>56000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E22" s="3">
         <v>15000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>18000</v>
       </c>
       <c r="H22" s="3">
         <v>18000</v>
       </c>
       <c r="I22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="J22" s="3">
         <v>15000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>11000</v>
       </c>
       <c r="L22" s="3">
         <v>11000</v>
       </c>
       <c r="M22" s="3">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="N22" s="3">
         <v>12000</v>
       </c>
       <c r="O22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="P22" s="3">
         <v>13000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>14000</v>
       </c>
       <c r="Q22" s="3">
         <v>14000</v>
       </c>
       <c r="R22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="S22" s="3">
         <v>18000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>17000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>16000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>17000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20000</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1945,186 +1985,195 @@
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E23" s="3">
         <v>101000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>37000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>94000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>81000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>70000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>96000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>131000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>121000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>102000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>97000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>81000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>73000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>97000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>82000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-53000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-25000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>84000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>38000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>79000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>22000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>58000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>39000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E24" s="3">
         <v>19000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>44000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>24000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>31000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>33000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>37000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>34000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>35000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>23000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>24000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>38000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>23000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1000</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>36000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>339100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-329000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>34000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>18000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>35000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>23000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2212,186 +2261,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E26" s="3">
         <v>82000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>50000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>57000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>39000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>63000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>94000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>87000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>67000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>68000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>58000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>49000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>59000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>75000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-76000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-21000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>48000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-301100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>311000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>30000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>45000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>23000</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>16000</v>
       </c>
       <c r="AE26" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E27" s="3">
         <v>82000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>50000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>57000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>39000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>63000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>94000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>87000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>67000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>68000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>58000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>49000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>59000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>75000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-76000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-21000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>48000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-301100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>311000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>30000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>45000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>23000</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>16000</v>
       </c>
       <c r="AE27" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2479,8 +2537,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2526,8 +2587,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2544,32 +2605,35 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>317100</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>3000</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-453000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2657,8 +2721,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2746,82 +2813,85 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-19000</v>
+        <v>-1000</v>
       </c>
       <c r="E32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F32" s="3">
         <v>13000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2000</v>
       </c>
       <c r="G32" s="3">
         <v>-2000</v>
       </c>
       <c r="H32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-31000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>41000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>35000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>29000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>42000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>64000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>35000</v>
       </c>
       <c r="V32" s="3">
         <v>35000</v>
       </c>
       <c r="W32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="X32" s="3">
         <v>-16000</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB32" s="3">
         <v>-1000</v>
@@ -2830,102 +2900,108 @@
         <v>-1000</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E33" s="3">
         <v>82000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>50000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>57000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>39000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>63000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>94000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>87000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>67000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>68000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>58000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>49000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>59000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>75000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-76000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-21000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>48000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>16000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>311000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>33000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>45000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-449000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>23000</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>16000</v>
       </c>
       <c r="AE33" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3013,191 +3089,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E35" s="3">
         <v>82000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>50000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>57000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>39000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>63000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>94000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>87000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>67000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>68000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>58000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>49000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>59000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>75000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-76000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-21000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>48000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>16000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>311000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>33000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>45000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-449000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>23000</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>16000</v>
       </c>
       <c r="AE35" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3229,8 +3314,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3262,86 +3348,87 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>603000</v>
+      </c>
+      <c r="E41" s="3">
         <v>636000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>368000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>381000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>292000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>326000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>252000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>251000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>244000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>779000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>686000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>579000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>508000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>517000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>260000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>362000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>338000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>122000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>132000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>142000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>212000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>265000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>184000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>93000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>75000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3351,8 +3438,11 @@
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3440,86 +3530,89 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>933000</v>
+      </c>
+      <c r="E43" s="3">
         <v>973000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>988000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1043000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>985000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1002000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1043000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1073000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1008000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>876000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>932000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>895000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>875000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>863000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>884000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>704000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>820000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>817000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>845000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>835000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>838000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>821000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>809000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>766000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>756000</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3529,86 +3622,89 @@
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>929000</v>
+      </c>
+      <c r="E44" s="3">
         <v>941000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>970000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1001000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1008000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>975000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>957000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>971000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>922000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>740000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>710000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>684000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>681000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>672000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>618000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>614000</v>
-      </c>
-      <c r="S44" s="3">
-        <v>671000</v>
       </c>
       <c r="T44" s="3">
         <v>671000</v>
       </c>
       <c r="U44" s="3">
+        <v>671000</v>
+      </c>
+      <c r="V44" s="3">
         <v>729000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>722000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>701000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>628000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>603000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>523000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>481000</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3618,86 +3714,89 @@
       <c r="AE44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E45" s="3">
         <v>193000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>289000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>197000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>210000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>199000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>198000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>186000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>165000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>146000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>179000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>198000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>156000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>173000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>161000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>163000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>164000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>175000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>134000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>147000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>111000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>95000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>72000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>74000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>65000</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3707,86 +3806,89 @@
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2677000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2743000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2615000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2622000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2495000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2502000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2450000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2481000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2339000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2541000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2507000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2356000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2220000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2225000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1923000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1843000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1993000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1785000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1840000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1846000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1862000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1809000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1668000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1456000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1377000</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3796,8 +3898,11 @@
       <c r="AE46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3885,86 +3990,89 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>552000</v>
+      </c>
+      <c r="E48" s="3">
         <v>582000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>577000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>580000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>571000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>557000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>538000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>535000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>514000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>428000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>424000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>438000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>442000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>451000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>445000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>440000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>433000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>453000</v>
-      </c>
-      <c r="U48" s="3">
-        <v>436000</v>
       </c>
       <c r="V48" s="3">
         <v>436000</v>
       </c>
       <c r="W48" s="3">
+        <v>436000</v>
+      </c>
+      <c r="X48" s="3">
         <v>413000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>300000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>276000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>264000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>267000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3974,86 +4082,89 @@
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3145000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3166000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3143000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3204000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3207000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3199000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3138000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3158000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3125000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2661000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2671000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2682000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2675000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2691000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2657000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2638000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2612000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2769000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2757000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2777000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2772000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2767000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2776000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2766000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2810000</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4063,8 +4174,11 @@
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4152,8 +4266,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4241,86 +4358,89 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E52" s="3">
         <v>154000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>124000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>130000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>126000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>129000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>136000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>142000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>267000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>223000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>232000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>236000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>239000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>243000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>244000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>245000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>249000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>121000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>100000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>101000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>97000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>96000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>22000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>21000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>28000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4330,8 +4450,11 @@
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4419,86 +4542,89 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6520000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6645000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6459000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6536000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6399000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6387000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6262000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6316000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6245000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5853000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5834000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5712000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5576000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5610000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5269000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5166000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5287000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5128000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5133000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5160000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5144000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4972000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4742000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4507000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4482000</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4508,8 +4634,11 @@
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4541,8 +4670,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4574,86 +4704,87 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>858000</v>
+      </c>
+      <c r="E57" s="3">
         <v>905000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>863000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>948000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>894000</v>
       </c>
       <c r="H57" s="3">
         <v>894000</v>
       </c>
       <c r="I57" s="3">
+        <v>894000</v>
+      </c>
+      <c r="J57" s="3">
         <v>936000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>987000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>958000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>883000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>905000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>915000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>908000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>936000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>858000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>811000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>906000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>920000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>932000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1009000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1013000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>964000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>850000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>774000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>712000</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4663,8 +4794,11 @@
       <c r="AE57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4693,7 +4827,7 @@
         <v>12000</v>
       </c>
       <c r="L58" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="M58" s="3">
         <v>10000</v>
@@ -4705,25 +4839,25 @@
         <v>10000</v>
       </c>
       <c r="P58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>7000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>181000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>287000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>382000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>22000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>88000</v>
-      </c>
-      <c r="V58" s="3">
-        <v>22000</v>
       </c>
       <c r="W58" s="3">
         <v>22000</v>
@@ -4731,8 +4865,8 @@
       <c r="X58" s="3">
         <v>22000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
+      <c r="Y58" s="3">
+        <v>22000</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>8</v>
@@ -4752,86 +4886,89 @@
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>515000</v>
+      </c>
+      <c r="E59" s="3">
         <v>608000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>592000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>564000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>563000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>640000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>594000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>580000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>576000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>601000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>617000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>586000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>528000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>595000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>606000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>564000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>467000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>552000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>531000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>528000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>524000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>503000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>550000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>459000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>418000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4841,86 +4978,89 @@
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1385000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1525000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1467000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1524000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1469000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1546000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1542000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1579000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1546000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1494000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1532000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1511000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1446000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1538000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1645000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1662000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1755000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1494000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1551000</v>
-      </c>
-      <c r="V60" s="3">
-        <v>1559000</v>
       </c>
       <c r="W60" s="3">
         <v>1559000</v>
       </c>
       <c r="X60" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="Y60" s="3">
         <v>1489000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1400000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1233000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1130000</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4930,77 +5070,80 @@
       <c r="AE60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1394000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1396000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1397000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1400000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1402000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1404000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1407000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1410000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1412000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1220000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1222000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1184000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1186000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1155000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1006000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1011000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1149000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1158000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1165000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1169000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1174000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1179000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5019,86 +5162,89 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>972000</v>
+      </c>
+      <c r="E62" s="3">
         <v>975000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>950000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>935000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>924000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>908000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>913000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>933000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>926000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>887000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>922000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>914000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>912000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>924000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1013000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>998000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>862000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>874000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>844000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>839000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>819000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>771000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>657000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>794000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>763000</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5108,8 +5254,11 @@
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5197,8 +5346,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5286,8 +5438,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5375,86 +5530,89 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3751000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3896000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3814000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3859000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3795000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3858000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3862000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3922000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3884000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3601000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3676000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3609000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3544000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3617000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3664000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3671000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3766000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3526000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3560000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3567000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3552000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3439000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2057000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2027000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1893000</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5464,8 +5622,11 @@
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5497,8 +5658,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5586,8 +5748,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5675,8 +5840,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5764,8 +5932,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5853,77 +6024,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>853000</v>
+      </c>
+      <c r="E72" s="3">
         <v>810000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>728000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>707000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>657000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>600000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>561000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>498000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>404000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>317000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>250000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>182000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>124000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>75000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-59000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>38000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>47000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>39000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>50000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5942,8 +6116,11 @@
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6031,8 +6208,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6120,8 +6300,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6209,86 +6392,89 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2769000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2749000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2645000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2677000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2604000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2529000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2400000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2394000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2361000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2252000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2158000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2103000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2032000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1993000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1605000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1495000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1521000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1602000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1573000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1593000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1592000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1533000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2685000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2480000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2589000</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6298,8 +6484,11 @@
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6387,191 +6576,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E81" s="3">
         <v>82000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>50000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>57000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>39000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>63000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>94000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>87000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>67000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>68000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>58000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>49000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>59000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>75000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-76000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-21000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>48000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>16000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>311000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>33000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>45000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-449000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>23000</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>16000</v>
       </c>
       <c r="AE81" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6603,85 +6801,86 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E83" s="3">
         <v>27000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>25000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>25000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>22000</v>
       </c>
       <c r="N83" s="3">
         <v>22000</v>
       </c>
       <c r="O83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="P83" s="3">
         <v>23000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>22000</v>
       </c>
       <c r="Q83" s="3">
         <v>22000</v>
       </c>
       <c r="R83" s="3">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="S83" s="3">
         <v>21000</v>
       </c>
       <c r="T83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="U83" s="3">
         <v>25000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>19000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>16000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>17000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>16000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>13000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20000</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>17000</v>
       </c>
       <c r="AC83" s="3">
         <v>17000</v>
@@ -6690,10 +6889,13 @@
         <v>17000</v>
       </c>
       <c r="AE83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6781,8 +6983,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6870,8 +7075,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6959,8 +7167,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7048,8 +7259,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7137,97 +7351,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E89" s="3">
         <v>263000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>60000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>121000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>139000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>37000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>35000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-59000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>112000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>104000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>94000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>152000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>145000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-74000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>93000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-33000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-27000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-10000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>87000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>117000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>132000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>126000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-143000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>111000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>30000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7259,97 +7479,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-29000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-51000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-29000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-28000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-23000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-40000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7437,8 +7661,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7526,97 +7753,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E94" s="3">
         <v>46000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-37000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-665000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-24000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-19000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-51000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-29000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-28000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-34000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-21000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-39000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7648,8 +7881,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7737,8 +7971,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7826,8 +8063,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7915,8 +8155,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8004,271 +8247,283 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-17000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-29000</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-9000</v>
       </c>
       <c r="G100" s="3">
         <v>-9000</v>
       </c>
       <c r="H100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-12000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>189000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>21000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>118000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-106000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-108000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>349000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-75000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>53000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-23000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>19000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>15000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-102000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>157000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-88000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-28000</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-25000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13000</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5000</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>2000</v>
       </c>
       <c r="R101" s="3">
         <v>2000</v>
       </c>
       <c r="S101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T101" s="3">
         <v>-8000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>2000</v>
       </c>
       <c r="AD101" s="3">
         <v>2000</v>
       </c>
       <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+        <v>2000</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E102" s="3">
         <v>267000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>87000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>74000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>11000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-535000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>93000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>107000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>71000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>257000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-102000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>24000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>216000</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-10000</v>
       </c>
       <c r="U102" s="3">
         <v>-10000</v>
       </c>
       <c r="V102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="W102" s="3">
         <v>-70000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-53000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>81000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>91000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>18000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>19000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>10000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
@@ -656,413 +656,426 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1589000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1486000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1537000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1554000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1602000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1549000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1560000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1618000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1686000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1506000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1454000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1496000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1477000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1419000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1501000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1362000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1029000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1179000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1304000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1226000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1242000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1216000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1266000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1200000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1196000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1165000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1209000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1152000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1096000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1062000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1142000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1086000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1114000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1137000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1166000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1129000</v>
       </c>
       <c r="I9" s="3">
         <v>1129000</v>
       </c>
       <c r="J9" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="K9" s="3">
         <v>1188000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1219000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1072000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1058000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1080000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1096000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1051000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1076000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>990000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>789000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>892000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>930000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>932000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>933000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>903000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>936000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>853000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>850000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>822000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>848000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>816000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>788000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>751000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>447000</v>
+      </c>
+      <c r="E10" s="3">
         <v>400000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>423000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>417000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>436000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>420000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>431000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>430000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>467000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>434000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>396000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>416000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>381000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>368000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>425000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>372000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>240000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>287000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>374000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>294000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>309000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>313000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>330000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>347000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>346000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>343000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>361000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>336000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>308000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>311000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1095,50 +1108,51 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>25000</v>
+        <v>21000</v>
       </c>
       <c r="E12" s="3">
         <v>25000</v>
       </c>
       <c r="F12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="G12" s="3">
         <v>28000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>29000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>27000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>28000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22000</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1187,8 +1201,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1279,82 +1296,85 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E14" s="3">
         <v>50000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>32000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>81000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>46000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>43000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>76000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>43000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>45000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>41000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>35000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>57000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>36000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>59000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>11000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>9000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-17000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>10000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>40000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1371,38 +1391,41 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E15" s="3">
         <v>9000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>10000</v>
       </c>
       <c r="J15" s="3">
         <v>10000</v>
       </c>
       <c r="K15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L15" s="3">
         <v>9000</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1418,8 +1441,8 @@
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1463,8 +1486,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1494,192 +1520,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1514000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1401000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1422000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1488000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1493000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1452000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1503000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1506000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1545000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1375000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1348000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1386000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1392000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1348000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1349000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1231000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1035000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1145000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1232000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1167000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1200000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1131000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1208000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1218000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1190000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1188000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1095000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1057000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1015000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E18" s="3">
         <v>85000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>115000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>66000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>109000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>97000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>57000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>112000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>141000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>131000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>106000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>110000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>85000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>71000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>152000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>131000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>34000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>72000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>59000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>42000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>85000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>58000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>78000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>21000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>57000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>39000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1712,85 +1745,86 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="E20" s="3">
         <v>1000</v>
       </c>
       <c r="F20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-13000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>2000</v>
       </c>
       <c r="H20" s="3">
         <v>2000</v>
       </c>
       <c r="I20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J20" s="3">
         <v>31000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-41000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-35000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-29000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-42000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-64000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-35000</v>
       </c>
       <c r="W20" s="3">
         <v>-35000</v>
       </c>
       <c r="X20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>16000</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>1000</v>
       </c>
       <c r="AC20" s="3">
         <v>1000</v>
@@ -1799,177 +1833,183 @@
         <v>1000</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E21" s="3">
         <v>110000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>143000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>75000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>136000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>123000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>113000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>135000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>170000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>152000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>134000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>131000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>115000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>109000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>133000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>118000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-14000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>33000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>43000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>27000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>117000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>75000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>21000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>96000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>39000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>75000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>56000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="3">
         <v>13000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>18000</v>
       </c>
       <c r="I22" s="3">
         <v>18000</v>
       </c>
       <c r="J22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="K22" s="3">
         <v>15000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>11000</v>
       </c>
       <c r="M22" s="3">
         <v>11000</v>
       </c>
       <c r="N22" s="3">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="O22" s="3">
         <v>12000</v>
       </c>
       <c r="P22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>13000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>14000</v>
       </c>
       <c r="R22" s="3">
         <v>14000</v>
       </c>
       <c r="S22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="T22" s="3">
         <v>18000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>17000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>17000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20000</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1988,192 +2028,201 @@
       <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E23" s="3">
         <v>73000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>101000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>37000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>94000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>81000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>70000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>96000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>131000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>121000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>102000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>97000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>81000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>73000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>97000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>82000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-53000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-25000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>84000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>38000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>79000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>22000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>58000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>39000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E24" s="3">
         <v>30000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>16000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>44000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>24000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>31000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>33000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>37000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>34000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>35000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>29000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>24000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>38000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1000</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>36000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>339100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-329000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>34000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>18000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>35000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>23000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2264,192 +2313,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E26" s="3">
         <v>43000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>82000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>50000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>57000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>39000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>63000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>94000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>87000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>67000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>68000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>58000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>49000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>59000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>75000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-76000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-21000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>48000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-301100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>311000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>30000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>45000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>23000</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>16000</v>
       </c>
       <c r="AF26" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E27" s="3">
         <v>43000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>82000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>50000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>57000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>39000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>63000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>94000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>87000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>67000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>68000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>58000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>49000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>59000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>75000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-76000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-21000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>48000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-301100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>311000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>30000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>45000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>23000</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>16000</v>
       </c>
       <c r="AF27" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2540,8 +2598,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2590,8 +2651,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2608,32 +2669,35 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>317100</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>3000</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-453000</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2724,8 +2788,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2816,85 +2883,88 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="3">
         <v>-1000</v>
       </c>
       <c r="F32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G32" s="3">
         <v>13000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-2000</v>
       </c>
       <c r="H32" s="3">
         <v>-2000</v>
       </c>
       <c r="I32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-31000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>41000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>35000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>29000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>42000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>64000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>35000</v>
       </c>
       <c r="W32" s="3">
         <v>35000</v>
       </c>
       <c r="X32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AC32" s="3">
         <v>-1000</v>
@@ -2903,105 +2973,111 @@
         <v>-1000</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E33" s="3">
         <v>43000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>82000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>50000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>57000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>39000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>63000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>94000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>87000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>67000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>68000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>58000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>49000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>59000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>75000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-76000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-21000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>48000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>16000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>311000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>33000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>45000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-449000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>23000</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>16000</v>
       </c>
       <c r="AF33" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3092,197 +3168,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E35" s="3">
         <v>43000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>82000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>50000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>57000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>39000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>63000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>94000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>87000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>67000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>68000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>58000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>49000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>59000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>75000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-76000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-21000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>48000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>16000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>311000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>33000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>45000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-449000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>23000</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>16000</v>
       </c>
       <c r="AF35" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3315,8 +3400,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3349,89 +3435,90 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>413000</v>
+      </c>
+      <c r="E41" s="3">
         <v>603000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>636000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>368000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>381000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>292000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>326000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>252000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>251000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>244000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>779000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>686000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>579000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>508000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>517000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>260000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>362000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>338000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>122000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>132000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>142000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>212000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>265000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>184000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>93000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>75000</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3441,8 +3528,11 @@
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3533,89 +3623,92 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1071000</v>
+      </c>
+      <c r="E43" s="3">
         <v>933000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>973000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>988000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1043000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>985000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1002000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1043000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1073000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1008000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>876000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>932000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>895000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>875000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>863000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>884000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>704000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>820000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>817000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>845000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>835000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>838000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>821000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>809000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>766000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>756000</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3625,89 +3718,92 @@
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1188000</v>
+      </c>
+      <c r="E44" s="3">
         <v>929000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>941000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>970000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1001000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1008000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>975000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>957000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>971000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>922000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>740000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>710000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>684000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>681000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>672000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>618000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>614000</v>
-      </c>
-      <c r="T44" s="3">
-        <v>671000</v>
       </c>
       <c r="U44" s="3">
         <v>671000</v>
       </c>
       <c r="V44" s="3">
+        <v>671000</v>
+      </c>
+      <c r="W44" s="3">
         <v>729000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>722000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>701000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>628000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>603000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>523000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>481000</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3717,8 +3813,11 @@
       <c r="AF44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3726,80 +3825,80 @@
         <v>212000</v>
       </c>
       <c r="E45" s="3">
+        <v>212000</v>
+      </c>
+      <c r="F45" s="3">
         <v>193000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>289000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>197000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>210000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>199000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>198000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>186000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>165000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>146000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>179000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>198000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>156000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>173000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>161000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>163000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>164000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>175000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>134000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>147000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>111000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>95000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>72000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>74000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>65000</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3809,89 +3908,92 @@
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2884000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2677000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2743000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2615000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2622000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2495000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2502000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2450000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2481000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2339000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2541000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2507000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2356000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2220000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2225000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1923000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1843000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1993000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1785000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1840000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1846000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1862000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1809000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1668000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1456000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1377000</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3901,8 +4003,11 @@
       <c r="AF46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3993,89 +4098,92 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>658000</v>
+      </c>
+      <c r="E48" s="3">
         <v>552000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>582000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>577000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>580000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>571000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>557000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>538000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>535000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>514000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>428000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>424000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>438000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>442000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>451000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>445000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>440000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>433000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>453000</v>
-      </c>
-      <c r="V48" s="3">
-        <v>436000</v>
       </c>
       <c r="W48" s="3">
         <v>436000</v>
       </c>
       <c r="X48" s="3">
+        <v>436000</v>
+      </c>
+      <c r="Y48" s="3">
         <v>413000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>300000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>276000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>264000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>267000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4085,89 +4193,92 @@
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4297000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3145000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3166000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3143000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3204000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3207000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3199000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3138000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3158000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3125000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2661000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2671000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2682000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2675000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2691000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2657000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2638000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2612000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2769000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2757000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2777000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2772000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2767000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2776000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2766000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2810000</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4177,8 +4288,11 @@
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4269,8 +4383,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4361,89 +4478,92 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E52" s="3">
         <v>146000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>154000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>124000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>130000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>126000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>129000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>136000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>142000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>267000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>223000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>232000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>236000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>239000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>243000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>244000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>245000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>249000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>121000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>100000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>101000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>97000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>96000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>22000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>21000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>28000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4453,8 +4573,11 @@
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4545,89 +4668,92 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7984000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6520000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6645000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6459000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6536000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6399000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6387000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6262000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6316000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6245000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5853000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5834000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5712000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5576000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5610000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5269000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5166000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5287000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5128000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5133000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5160000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5144000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4972000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4742000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4507000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4482000</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4637,8 +4763,11 @@
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4671,8 +4800,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4705,89 +4835,90 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>980000</v>
+      </c>
+      <c r="E57" s="3">
         <v>858000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>905000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>863000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>948000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>894000</v>
       </c>
       <c r="I57" s="3">
         <v>894000</v>
       </c>
       <c r="J57" s="3">
+        <v>894000</v>
+      </c>
+      <c r="K57" s="3">
         <v>936000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>987000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>958000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>883000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>905000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>915000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>908000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>936000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>858000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>811000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>906000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>920000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>932000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1009000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1013000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>964000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>850000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>774000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>712000</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4797,8 +4928,11 @@
       <c r="AF57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4830,7 +4964,7 @@
         <v>12000</v>
       </c>
       <c r="M58" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="N58" s="3">
         <v>10000</v>
@@ -4842,25 +4976,25 @@
         <v>10000</v>
       </c>
       <c r="Q58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="R58" s="3">
         <v>7000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>181000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>287000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>382000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>22000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>88000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>22000</v>
       </c>
       <c r="X58" s="3">
         <v>22000</v>
@@ -4868,8 +5002,8 @@
       <c r="Y58" s="3">
         <v>22000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
+      <c r="Z58" s="3">
+        <v>22000</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>8</v>
@@ -4889,89 +5023,92 @@
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>602000</v>
+      </c>
+      <c r="E59" s="3">
         <v>515000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>608000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>592000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>564000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>563000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>640000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>594000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>580000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>576000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>601000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>617000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>586000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>528000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>595000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>606000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>564000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>467000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>552000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>531000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>528000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>524000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>503000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>550000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>459000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>418000</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4981,89 +5118,92 @@
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1594000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1385000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1525000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1467000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1524000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1469000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1546000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1542000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1579000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1546000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1494000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1532000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1511000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1446000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1538000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1645000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1662000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1755000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1494000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1551000</v>
-      </c>
-      <c r="W60" s="3">
-        <v>1559000</v>
       </c>
       <c r="X60" s="3">
         <v>1559000</v>
       </c>
       <c r="Y60" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="Z60" s="3">
         <v>1489000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1400000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1233000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1130000</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5073,80 +5213,83 @@
       <c r="AF60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1979000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1394000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1396000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1397000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1400000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1402000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1404000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1407000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1410000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1412000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1220000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1222000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1184000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1186000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1155000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1006000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1011000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1149000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1158000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1165000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1169000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1174000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1179000</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5165,89 +5308,92 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1116800</v>
+      </c>
+      <c r="E62" s="3">
         <v>972000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>975000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>950000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>935000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>924000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>908000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>913000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>933000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>926000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>887000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>922000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>914000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>912000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>924000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1013000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>998000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>862000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>874000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>844000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>839000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>819000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>771000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>657000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>794000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>763000</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5257,8 +5403,11 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5349,8 +5498,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5441,8 +5593,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5533,89 +5688,92 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4689800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3751000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3896000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3814000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3859000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3795000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3858000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3862000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3922000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3884000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3601000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3676000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3609000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3544000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3617000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3664000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3671000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3766000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3526000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3560000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3567000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3552000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3439000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2057000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2027000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1893000</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5625,8 +5783,11 @@
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5659,8 +5820,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5751,8 +5913,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5843,13 +6008,16 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>482000</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -5935,8 +6103,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6027,80 +6198,83 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>881000</v>
+      </c>
+      <c r="E72" s="3">
         <v>853000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>810000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>728000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>707000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>657000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>600000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>561000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>498000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>404000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>317000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>250000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>182000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>124000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>75000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-59000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>38000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>47000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>39000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>50000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2000</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6119,8 +6293,11 @@
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6211,8 +6388,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6303,8 +6483,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6395,89 +6578,92 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2812200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2769000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2749000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2645000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2677000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2604000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2529000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2400000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2394000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2361000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2252000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2158000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2103000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2032000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1993000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1605000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1495000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1521000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1602000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1573000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1593000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1592000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1533000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2685000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2480000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2589000</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6487,8 +6673,11 @@
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6579,197 +6768,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E81" s="3">
         <v>43000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>82000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>50000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>57000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>39000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>63000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>94000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>87000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>67000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>68000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>58000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>49000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>59000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>75000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-76000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-21000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>48000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>16000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>311000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>33000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>45000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-449000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>23000</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>16000</v>
       </c>
       <c r="AF81" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6802,88 +7000,89 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E83" s="3">
         <v>24000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>27000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>22000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>22000</v>
       </c>
       <c r="O83" s="3">
         <v>22000</v>
       </c>
       <c r="P83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>23000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>22000</v>
       </c>
       <c r="R83" s="3">
         <v>22000</v>
       </c>
       <c r="S83" s="3">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="T83" s="3">
         <v>21000</v>
       </c>
       <c r="U83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="V83" s="3">
         <v>25000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>19000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>16000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>17000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>16000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>13000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>20000</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>17000</v>
       </c>
       <c r="AD83" s="3">
         <v>17000</v>
@@ -6892,10 +7091,13 @@
         <v>17000</v>
       </c>
       <c r="AF83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AG83" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6986,8 +7188,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7078,8 +7283,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7170,8 +7378,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7262,8 +7473,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7354,100 +7568,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>263000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>60000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>121000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>139000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>37000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>35000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-59000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>112000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>104000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>94000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>152000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>145000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-74000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>93000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-33000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-27000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>87000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>117000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>132000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>126000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-143000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>111000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>30000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7480,100 +7700,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-29000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-51000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-29000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-28000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-23000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7664,8 +7888,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7756,100 +7983,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1342000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>46000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-57000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-37000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-665000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-18000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-51000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-29000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-28000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-34000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-39000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7882,8 +8115,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7974,8 +8208,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8066,8 +8303,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8158,8 +8398,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8250,280 +8493,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1060000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-17000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-29000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-9000</v>
       </c>
       <c r="H100" s="3">
         <v>-9000</v>
       </c>
       <c r="I100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="J100" s="3">
         <v>-12000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>189000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>21000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>13000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>118000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-106000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-108000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>349000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-75000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>53000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>19000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>15000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-102000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>157000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-88000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-28000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-25000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-13000</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>2000</v>
       </c>
       <c r="S101" s="3">
         <v>2000</v>
       </c>
       <c r="T101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U101" s="3">
         <v>-8000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>2000</v>
       </c>
       <c r="AE101" s="3">
         <v>2000</v>
       </c>
       <c r="AF101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+        <v>2000</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-190000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-33000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>267000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>87000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>74000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>11000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-535000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>93000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>107000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>71000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>257000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-102000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>24000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>216000</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-10000</v>
       </c>
       <c r="V102" s="3">
         <v>-10000</v>
       </c>
       <c r="W102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="X102" s="3">
         <v>-70000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-53000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>81000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>91000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>18000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>19000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>10000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
   <si>
     <t>REZI</t>
   </si>
@@ -656,426 +656,439 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1828000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1589000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1486000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1537000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1554000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1602000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1549000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1560000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1618000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1686000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1506000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1454000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1496000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1477000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1419000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1501000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1362000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1029000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1179000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1304000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1226000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1242000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1216000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1266000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1200000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1196000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1165000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1209000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1152000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1096000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1062000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1304000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1142000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1086000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1114000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1137000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1166000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
+        <v>1131000</v>
+      </c>
+      <c r="K9" s="3">
         <v>1129000</v>
       </c>
-      <c r="J9" s="3">
-        <v>1129000</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1188000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1219000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1072000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1058000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1080000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1096000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1051000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1076000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>990000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>789000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>892000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>930000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>932000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>933000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>903000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>936000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>853000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>850000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>822000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>848000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>816000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>788000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>751000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>524000</v>
+      </c>
+      <c r="E10" s="3">
         <v>447000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>400000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>423000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>417000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>436000</v>
       </c>
-      <c r="I10" s="3">
-        <v>420000</v>
-      </c>
       <c r="J10" s="3">
+        <v>418000</v>
+      </c>
+      <c r="K10" s="3">
         <v>431000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>430000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>467000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>434000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>396000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>416000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>381000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>368000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>425000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>372000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>240000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>287000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>374000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>294000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>309000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>313000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>330000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>347000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>346000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>343000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>361000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>336000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>308000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>311000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1109,53 +1122,54 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E12" s="3">
         <v>21000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>25000</v>
       </c>
       <c r="F12" s="3">
         <v>25000</v>
       </c>
       <c r="G12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="H12" s="3">
         <v>28000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29000</v>
       </c>
-      <c r="I12" s="3">
-        <v>27000</v>
-      </c>
       <c r="J12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="K12" s="3">
         <v>30000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>28000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>22000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1204,8 +1218,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,85 +1316,88 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>92000</v>
+        <v>74000</v>
       </c>
       <c r="E14" s="3">
+        <v>58000</v>
+      </c>
+      <c r="F14" s="3">
         <v>50000</v>
       </c>
-      <c r="F14" s="3">
-        <v>32000</v>
-      </c>
       <c r="G14" s="3">
+        <v>50000</v>
+      </c>
+      <c r="H14" s="3">
         <v>81000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>46000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>76000</v>
+      </c>
+      <c r="L14" s="3">
         <v>43000</v>
       </c>
-      <c r="J14" s="3">
-        <v>76000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>43000</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>45000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>41000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>35000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>57000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>36000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>59000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>13000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>11000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>9000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-17000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>10000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>40000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1394,41 +1414,44 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E15" s="3">
         <v>13000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>10000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>10000</v>
       </c>
       <c r="K15" s="3">
         <v>10000</v>
       </c>
       <c r="L15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="M15" s="3">
         <v>9000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1444,8 +1467,8 @@
       <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1489,8 +1512,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1521,198 +1547,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1514000</v>
+        <v>1673000</v>
       </c>
       <c r="E17" s="3">
-        <v>1401000</v>
+        <v>1456000</v>
       </c>
       <c r="F17" s="3">
-        <v>1422000</v>
+        <v>1351000</v>
       </c>
       <c r="G17" s="3">
-        <v>1488000</v>
+        <v>1381000</v>
       </c>
       <c r="H17" s="3">
-        <v>1493000</v>
+        <v>1407000</v>
       </c>
       <c r="I17" s="3">
-        <v>1452000</v>
+        <v>1447000</v>
       </c>
       <c r="J17" s="3">
+        <v>1409000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1503000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1506000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1545000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1375000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1348000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1386000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1392000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1348000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1349000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1231000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1035000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1145000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1232000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1167000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1200000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1131000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1208000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1218000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1190000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1188000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1095000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1057000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1015000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>75000</v>
+        <v>155000</v>
       </c>
       <c r="E18" s="3">
+        <v>133000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>135000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>156000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>147000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>155000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>140000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>57000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>112000</v>
+      </c>
+      <c r="M18" s="3">
+        <v>141000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>131000</v>
+      </c>
+      <c r="O18" s="3">
+        <v>106000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>110000</v>
+      </c>
+      <c r="Q18" s="3">
         <v>85000</v>
       </c>
-      <c r="F18" s="3">
-        <v>115000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>66000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>109000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>97000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="R18" s="3">
+        <v>71000</v>
+      </c>
+      <c r="S18" s="3">
+        <v>152000</v>
+      </c>
+      <c r="T18" s="3">
+        <v>131000</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="V18" s="3">
+        <v>34000</v>
+      </c>
+      <c r="W18" s="3">
+        <v>72000</v>
+      </c>
+      <c r="X18" s="3">
+        <v>59000</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>42000</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>85000</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>78000</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AF18" s="3">
         <v>57000</v>
       </c>
-      <c r="K18" s="3">
-        <v>112000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>141000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>131000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>106000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>110000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>85000</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>71000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>152000</v>
-      </c>
-      <c r="S18" s="3">
-        <v>131000</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="U18" s="3">
-        <v>34000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>72000</v>
-      </c>
-      <c r="W18" s="3">
-        <v>59000</v>
-      </c>
-      <c r="X18" s="3">
-        <v>42000</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>85000</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>58000</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-18000</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>6000</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>78000</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>21000</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>57000</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>39000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1746,88 +1779,89 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1000</v>
+        <v>10000</v>
       </c>
       <c r="E20" s="3">
         <v>1000</v>
       </c>
       <c r="F20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>40000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>31000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>31000</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="O20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
-        <v>4000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>7000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>15000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-41000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-35000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-29000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-42000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-64000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-35000</v>
       </c>
       <c r="X20" s="3">
         <v>-35000</v>
       </c>
       <c r="Y20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>16000</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>1000</v>
       </c>
       <c r="AD20" s="3">
         <v>1000</v>
@@ -1836,183 +1870,189 @@
         <v>1000</v>
       </c>
       <c r="AF20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>102000</v>
+        <v>174000</v>
       </c>
       <c r="E21" s="3">
-        <v>110000</v>
+        <v>145000</v>
       </c>
       <c r="F21" s="3">
+        <v>145000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>176000</v>
+      </c>
+      <c r="H21" s="3">
         <v>143000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
+        <v>167000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>109000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>113000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>135000</v>
+      </c>
+      <c r="M21" s="3">
+        <v>170000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>152000</v>
+      </c>
+      <c r="O21" s="3">
+        <v>134000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>131000</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>115000</v>
+      </c>
+      <c r="R21" s="3">
+        <v>109000</v>
+      </c>
+      <c r="S21" s="3">
+        <v>133000</v>
+      </c>
+      <c r="T21" s="3">
+        <v>118000</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="V21" s="3">
+        <v>13000</v>
+      </c>
+      <c r="W21" s="3">
+        <v>33000</v>
+      </c>
+      <c r="X21" s="3">
+        <v>43000</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>27000</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>117000</v>
+      </c>
+      <c r="AA21" s="3">
         <v>75000</v>
       </c>
-      <c r="H21" s="3">
-        <v>136000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>123000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>113000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>135000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>170000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>152000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>134000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>131000</v>
-      </c>
-      <c r="P21" s="3">
-        <v>115000</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>109000</v>
-      </c>
-      <c r="R21" s="3">
-        <v>133000</v>
-      </c>
-      <c r="S21" s="3">
-        <v>118000</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="U21" s="3">
-        <v>13000</v>
-      </c>
-      <c r="V21" s="3">
-        <v>33000</v>
-      </c>
-      <c r="W21" s="3">
-        <v>43000</v>
-      </c>
-      <c r="X21" s="3">
-        <v>27000</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>117000</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>39000</v>
+      </c>
+      <c r="AF21" s="3">
         <v>75000</v>
       </c>
-      <c r="AA21" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>21000</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>96000</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>39000</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>75000</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>56000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E22" s="3">
         <v>15000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K22" s="3">
         <v>18000</v>
       </c>
-      <c r="J22" s="3">
-        <v>18000</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>11000</v>
       </c>
       <c r="N22" s="3">
         <v>11000</v>
       </c>
       <c r="O22" s="3">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="P22" s="3">
         <v>12000</v>
       </c>
       <c r="Q22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="R22" s="3">
         <v>13000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>14000</v>
       </c>
       <c r="S22" s="3">
         <v>14000</v>
       </c>
       <c r="T22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="U22" s="3">
         <v>18000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>17000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>18000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20000</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2031,198 +2071,207 @@
       <c r="AG22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E23" s="3">
         <v>59000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>73000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>101000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>37000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>94000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>81000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>70000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>96000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>131000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>121000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>102000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>97000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>81000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>73000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>97000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>82000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-53000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-25000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>84000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>38000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>79000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>22000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>58000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>39000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E24" s="3">
         <v>29000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>30000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>19000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>44000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>24000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>31000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>33000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>37000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>34000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>35000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>29000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>38000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>23000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1000</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>36000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>339100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-329000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>34000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>18000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>35000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>23000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2316,198 +2365,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E26" s="3">
         <v>30000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>43000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>82000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>50000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>57000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>39000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>63000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>94000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>87000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>67000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>68000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>58000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>49000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>59000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>75000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-76000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-21000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>8000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>48000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-301100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>311000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>30000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>45000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>23000</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>16000</v>
       </c>
       <c r="AG26" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>28000</v>
+        <v>11000</v>
       </c>
       <c r="E27" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F27" s="3">
         <v>43000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>82000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>50000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>57000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>39000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>63000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>94000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>87000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>67000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>68000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>58000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>49000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>59000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>75000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-76000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-21000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>48000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-301100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>311000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>30000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>45000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>23000</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>16000</v>
       </c>
       <c r="AG27" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2601,8 +2659,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2654,8 +2715,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2672,32 +2733,35 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>317100</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>3000</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-453000</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2791,8 +2855,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2886,88 +2953,91 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1000</v>
+        <v>-10000</v>
       </c>
       <c r="E32" s="3">
         <v>-1000</v>
       </c>
       <c r="F32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-31000</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="O32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-15000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>41000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>35000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>29000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>42000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>64000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>35000</v>
       </c>
       <c r="X32" s="3">
         <v>35000</v>
       </c>
       <c r="Y32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AD32" s="3">
         <v>-1000</v>
@@ -2976,108 +3046,114 @@
         <v>-1000</v>
       </c>
       <c r="AF32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>28000</v>
+        <v>20000</v>
       </c>
       <c r="E33" s="3">
+        <v>30000</v>
+      </c>
+      <c r="F33" s="3">
         <v>43000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>82000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>50000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>57000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>39000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>63000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>94000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>87000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>67000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>68000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>58000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>49000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>59000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>75000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-76000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-21000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>48000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>16000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>311000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>33000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>45000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-449000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>23000</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>16000</v>
       </c>
       <c r="AG33" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3171,203 +3247,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>28000</v>
+        <v>20000</v>
       </c>
       <c r="E35" s="3">
+        <v>30000</v>
+      </c>
+      <c r="F35" s="3">
         <v>43000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>82000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>50000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>57000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>39000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>63000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>94000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>87000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>67000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>68000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>58000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>49000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>59000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>75000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-76000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-21000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>48000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>16000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>311000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>33000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>45000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-449000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>23000</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>16000</v>
       </c>
       <c r="AG35" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3401,8 +3486,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3436,92 +3522,93 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E41" s="3">
         <v>413000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>603000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>636000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>368000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>381000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>292000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>326000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>252000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>251000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>244000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>779000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>686000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>579000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>508000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>517000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>260000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>362000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>338000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>122000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>132000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>142000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>212000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>265000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>184000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>93000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>75000</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3531,31 +3618,34 @@
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3626,92 +3716,95 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1103000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1071000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>933000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>973000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>988000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1043000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>985000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1002000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1043000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1073000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1008000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>876000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>932000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>895000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>875000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>863000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>884000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>704000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>820000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>817000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>845000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>835000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>838000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>821000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>809000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>766000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>756000</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3721,92 +3814,95 @@
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1197000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1188000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>929000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>941000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>970000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1001000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1008000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>975000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>957000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>971000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>922000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>740000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>710000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>684000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>681000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>672000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>618000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>614000</v>
-      </c>
-      <c r="U44" s="3">
-        <v>671000</v>
       </c>
       <c r="V44" s="3">
         <v>671000</v>
       </c>
       <c r="W44" s="3">
+        <v>671000</v>
+      </c>
+      <c r="X44" s="3">
         <v>729000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>722000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>701000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>628000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>603000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>523000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>481000</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3816,92 +3912,95 @@
       <c r="AG44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>212000</v>
+        <v>193000</v>
       </c>
       <c r="E45" s="3">
-        <v>212000</v>
+        <v>193000</v>
       </c>
       <c r="F45" s="3">
-        <v>193000</v>
+        <v>192000</v>
       </c>
       <c r="G45" s="3">
-        <v>289000</v>
+        <v>173000</v>
       </c>
       <c r="H45" s="3">
-        <v>197000</v>
+        <v>266000</v>
       </c>
       <c r="I45" s="3">
-        <v>210000</v>
+        <v>174000</v>
       </c>
       <c r="J45" s="3">
+        <v>189000</v>
+      </c>
+      <c r="K45" s="3">
         <v>199000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>198000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>186000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>165000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>146000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>179000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>198000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>156000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>173000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>161000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>163000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>164000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>175000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>134000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>147000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>111000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>95000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>72000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>74000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>65000</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3911,92 +4010,95 @@
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3037000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2884000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2677000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2743000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2615000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2622000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2495000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2502000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2450000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2481000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2339000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2541000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2507000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2356000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2220000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2225000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1923000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1843000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1993000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1785000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1840000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1846000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1862000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1809000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1668000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1456000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1377000</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4006,31 +4108,34 @@
       <c r="AG46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4101,92 +4206,95 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>648000</v>
+      </c>
+      <c r="E48" s="3">
         <v>658000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>552000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>582000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>577000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>580000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>571000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>557000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>538000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>535000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>514000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>428000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>424000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>438000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>442000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>451000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>445000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>440000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>433000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>453000</v>
-      </c>
-      <c r="W48" s="3">
-        <v>436000</v>
       </c>
       <c r="X48" s="3">
         <v>436000</v>
       </c>
       <c r="Y48" s="3">
+        <v>436000</v>
+      </c>
+      <c r="Z48" s="3">
         <v>413000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>300000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>276000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>264000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>267000</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4196,92 +4304,95 @@
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4316000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4297000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3145000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3166000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3143000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3204000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3207000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3199000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3138000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3158000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3125000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2661000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2671000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2682000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2675000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2691000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2657000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2638000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2612000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2769000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2757000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2777000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2772000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2767000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2776000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2766000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2810000</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4291,8 +4402,11 @@
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4386,8 +4500,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,92 +4598,95 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>145000</v>
+        <v>132000</v>
       </c>
       <c r="E52" s="3">
-        <v>146000</v>
+        <v>137000</v>
       </c>
       <c r="F52" s="3">
-        <v>154000</v>
+        <v>136000</v>
       </c>
       <c r="G52" s="3">
-        <v>124000</v>
+        <v>144000</v>
       </c>
       <c r="H52" s="3">
-        <v>130000</v>
+        <v>106000</v>
       </c>
       <c r="I52" s="3">
-        <v>126000</v>
+        <v>110000</v>
       </c>
       <c r="J52" s="3">
+        <v>109000</v>
+      </c>
+      <c r="K52" s="3">
         <v>129000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>136000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>142000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>267000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>223000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>232000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>236000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>239000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>243000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>244000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>245000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>249000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>121000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>100000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>101000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>97000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>96000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>22000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>21000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>28000</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4576,8 +4696,11 @@
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4671,92 +4794,95 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8135000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7984000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6520000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6645000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6459000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6536000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6399000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6387000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6262000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6316000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6245000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5853000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5834000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5712000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5576000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5610000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5269000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5166000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5287000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5128000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5133000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5160000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5144000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4972000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4742000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4507000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4482000</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4766,8 +4892,11 @@
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4801,8 +4930,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4836,92 +4966,93 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1021000</v>
+      </c>
+      <c r="E57" s="3">
         <v>980000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>858000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>905000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>863000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>948000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>894000</v>
       </c>
       <c r="J57" s="3">
         <v>894000</v>
       </c>
       <c r="K57" s="3">
+        <v>894000</v>
+      </c>
+      <c r="L57" s="3">
         <v>936000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>987000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>958000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>883000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>905000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>915000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>908000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>936000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>858000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>811000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>906000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>920000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>932000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1009000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1013000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>964000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>850000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>774000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>712000</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4931,31 +5062,34 @@
       <c r="AG57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12000</v>
+        <v>56000</v>
       </c>
       <c r="E58" s="3">
-        <v>12000</v>
+        <v>64000</v>
       </c>
       <c r="F58" s="3">
-        <v>12000</v>
+        <v>50000</v>
       </c>
       <c r="G58" s="3">
-        <v>12000</v>
+        <v>51000</v>
       </c>
       <c r="H58" s="3">
-        <v>12000</v>
+        <v>48000</v>
       </c>
       <c r="I58" s="3">
-        <v>12000</v>
+        <v>50000</v>
       </c>
       <c r="J58" s="3">
-        <v>12000</v>
+        <v>50000</v>
       </c>
       <c r="K58" s="3">
         <v>12000</v>
@@ -4967,7 +5101,7 @@
         <v>12000</v>
       </c>
       <c r="N58" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="O58" s="3">
         <v>10000</v>
@@ -4979,25 +5113,25 @@
         <v>10000</v>
       </c>
       <c r="R58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="S58" s="3">
         <v>7000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>181000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>287000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>382000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>22000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>88000</v>
-      </c>
-      <c r="X58" s="3">
-        <v>22000</v>
       </c>
       <c r="Y58" s="3">
         <v>22000</v>
@@ -5005,8 +5139,8 @@
       <c r="Z58" s="3">
         <v>22000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
+      <c r="AA58" s="3">
+        <v>22000</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>8</v>
@@ -5026,92 +5160,95 @@
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>602000</v>
+        <v>236000</v>
       </c>
       <c r="E59" s="3">
-        <v>515000</v>
+        <v>196000</v>
       </c>
       <c r="F59" s="3">
-        <v>608000</v>
+        <v>216000</v>
       </c>
       <c r="G59" s="3">
-        <v>592000</v>
+        <v>228000</v>
       </c>
       <c r="H59" s="3">
+        <v>212000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>198000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>210000</v>
+      </c>
+      <c r="K59" s="3">
+        <v>640000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>594000</v>
+      </c>
+      <c r="M59" s="3">
+        <v>580000</v>
+      </c>
+      <c r="N59" s="3">
+        <v>576000</v>
+      </c>
+      <c r="O59" s="3">
+        <v>601000</v>
+      </c>
+      <c r="P59" s="3">
+        <v>617000</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>586000</v>
+      </c>
+      <c r="R59" s="3">
+        <v>528000</v>
+      </c>
+      <c r="S59" s="3">
+        <v>595000</v>
+      </c>
+      <c r="T59" s="3">
+        <v>606000</v>
+      </c>
+      <c r="U59" s="3">
         <v>564000</v>
       </c>
-      <c r="I59" s="3">
-        <v>563000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>640000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>594000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>580000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>576000</v>
-      </c>
-      <c r="N59" s="3">
-        <v>601000</v>
-      </c>
-      <c r="O59" s="3">
-        <v>617000</v>
-      </c>
-      <c r="P59" s="3">
-        <v>586000</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="V59" s="3">
+        <v>467000</v>
+      </c>
+      <c r="W59" s="3">
+        <v>552000</v>
+      </c>
+      <c r="X59" s="3">
+        <v>531000</v>
+      </c>
+      <c r="Y59" s="3">
         <v>528000</v>
       </c>
-      <c r="R59" s="3">
-        <v>595000</v>
-      </c>
-      <c r="S59" s="3">
-        <v>606000</v>
-      </c>
-      <c r="T59" s="3">
-        <v>564000</v>
-      </c>
-      <c r="U59" s="3">
-        <v>467000</v>
-      </c>
-      <c r="V59" s="3">
-        <v>552000</v>
-      </c>
-      <c r="W59" s="3">
-        <v>531000</v>
-      </c>
-      <c r="X59" s="3">
-        <v>528000</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>524000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>503000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>550000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>459000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>418000</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5121,92 +5258,95 @@
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1672000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1594000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1385000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1525000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1467000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1524000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1469000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1546000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1542000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1579000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1546000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1494000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1532000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1511000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1446000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1538000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1645000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1662000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1755000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1494000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1551000</v>
-      </c>
-      <c r="X60" s="3">
-        <v>1559000</v>
       </c>
       <c r="Y60" s="3">
         <v>1559000</v>
       </c>
       <c r="Z60" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="AA60" s="3">
         <v>1489000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1400000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1233000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1130000</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5216,83 +5356,86 @@
       <c r="AG60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1979000</v>
+        <v>2177000</v>
       </c>
       <c r="E61" s="3">
-        <v>1394000</v>
+        <v>2181000</v>
       </c>
       <c r="F61" s="3">
-        <v>1396000</v>
+        <v>1553000</v>
       </c>
       <c r="G61" s="3">
-        <v>1397000</v>
+        <v>1562000</v>
       </c>
       <c r="H61" s="3">
-        <v>1400000</v>
+        <v>1571000</v>
       </c>
       <c r="I61" s="3">
-        <v>1402000</v>
+        <v>1566000</v>
       </c>
       <c r="J61" s="3">
+        <v>1568000</v>
+      </c>
+      <c r="K61" s="3">
         <v>1404000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1407000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1410000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1412000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1220000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1222000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1184000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1186000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1155000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1006000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1011000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1149000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1158000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1165000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1169000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1174000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1179000</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5311,92 +5454,95 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1116800</v>
+        <v>932000</v>
       </c>
       <c r="E62" s="3">
-        <v>972000</v>
+        <v>915000</v>
       </c>
       <c r="F62" s="3">
-        <v>975000</v>
+        <v>813000</v>
       </c>
       <c r="G62" s="3">
-        <v>950000</v>
+        <v>692000</v>
       </c>
       <c r="H62" s="3">
-        <v>935000</v>
+        <v>776000</v>
       </c>
       <c r="I62" s="3">
+        <v>769000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>758000</v>
+      </c>
+      <c r="K62" s="3">
+        <v>908000</v>
+      </c>
+      <c r="L62" s="3">
+        <v>913000</v>
+      </c>
+      <c r="M62" s="3">
+        <v>933000</v>
+      </c>
+      <c r="N62" s="3">
+        <v>926000</v>
+      </c>
+      <c r="O62" s="3">
+        <v>887000</v>
+      </c>
+      <c r="P62" s="3">
+        <v>922000</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>914000</v>
+      </c>
+      <c r="R62" s="3">
+        <v>912000</v>
+      </c>
+      <c r="S62" s="3">
         <v>924000</v>
       </c>
-      <c r="J62" s="3">
-        <v>908000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>913000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>933000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>926000</v>
-      </c>
-      <c r="N62" s="3">
-        <v>887000</v>
-      </c>
-      <c r="O62" s="3">
-        <v>922000</v>
-      </c>
-      <c r="P62" s="3">
-        <v>914000</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>912000</v>
-      </c>
-      <c r="R62" s="3">
-        <v>924000</v>
-      </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1013000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>998000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>862000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>874000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>844000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>839000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>819000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>771000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>657000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>794000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>763000</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5406,8 +5552,11 @@
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5501,8 +5650,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5596,8 +5748,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5691,92 +5846,95 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4689800</v>
+        <v>4781000</v>
       </c>
       <c r="E66" s="3">
+        <v>4690000</v>
+      </c>
+      <c r="F66" s="3">
         <v>3751000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3896000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3814000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3859000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3795000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3858000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3862000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3922000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3884000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3601000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3676000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3609000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3544000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3617000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3664000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3671000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3766000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3526000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3560000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3567000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3552000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3439000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2057000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2027000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1893000</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5786,8 +5944,11 @@
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5821,8 +5982,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5916,8 +6078,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6011,8 +6176,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6020,7 +6188,7 @@
         <v>482000</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>482000</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -6106,8 +6274,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6201,83 +6372,86 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>893000</v>
+      </c>
+      <c r="E72" s="3">
         <v>881000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>853000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>810000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>728000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>707000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>657000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>600000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>561000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>498000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>404000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>317000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>250000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>182000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>124000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>75000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-59000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>38000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>47000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>39000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>50000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2000</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6296,8 +6470,11 @@
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6391,8 +6568,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6486,8 +6666,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6581,92 +6764,95 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2812200</v>
+        <v>2872000</v>
       </c>
       <c r="E76" s="3">
+        <v>2812000</v>
+      </c>
+      <c r="F76" s="3">
         <v>2769000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2749000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2645000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2677000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2604000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2529000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2400000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2394000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2361000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2252000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2158000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2103000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2032000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1993000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1605000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1495000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1521000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1602000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1573000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1593000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1592000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1533000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2685000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2480000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2589000</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6676,8 +6862,11 @@
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6771,203 +6960,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>28000</v>
+        <v>20000</v>
       </c>
       <c r="E81" s="3">
+        <v>30000</v>
+      </c>
+      <c r="F81" s="3">
         <v>43000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>82000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>50000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>57000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>39000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>63000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>94000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>87000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>67000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>68000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>58000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>49000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>59000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>75000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-76000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-21000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>48000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>16000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>311000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>33000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>45000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-449000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>23000</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>16000</v>
       </c>
       <c r="AG81" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7001,91 +7199,92 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>28000</v>
+        <v>13000</v>
       </c>
       <c r="E83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F83" s="3">
         <v>24000</v>
       </c>
-      <c r="F83" s="3">
-        <v>27000</v>
-      </c>
       <c r="G83" s="3">
-        <v>22000</v>
+        <v>15000</v>
       </c>
       <c r="H83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K83" s="3">
         <v>25000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>24000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3">
         <v>25000</v>
       </c>
-      <c r="K83" s="3">
-        <v>24000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>25000</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>22000</v>
       </c>
       <c r="P83" s="3">
         <v>22000</v>
       </c>
       <c r="Q83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="R83" s="3">
         <v>23000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>22000</v>
       </c>
       <c r="S83" s="3">
         <v>22000</v>
       </c>
       <c r="T83" s="3">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="U83" s="3">
         <v>21000</v>
       </c>
       <c r="V83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="W83" s="3">
         <v>25000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>19000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>16000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>17000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>16000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>13000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>20000</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>17000</v>
       </c>
       <c r="AE83" s="3">
         <v>17000</v>
@@ -7094,10 +7293,13 @@
         <v>17000</v>
       </c>
       <c r="AG83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AH83" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7191,8 +7393,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7286,8 +7491,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7381,8 +7589,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7476,8 +7687,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7571,103 +7785,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E89" s="3">
         <v>92000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>263000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>60000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>121000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>139000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>37000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>35000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-59000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>112000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>104000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>94000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>152000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>145000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-74000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>93000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-33000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>87000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>117000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>132000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>126000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-143000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>111000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>30000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7701,103 +7921,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-21000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-25000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-29000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-51000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-29000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-28000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7891,8 +8115,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7986,103 +8213,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1342000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>46000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-35000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-57000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-37000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-665000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-24000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-51000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-29000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-28000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-39000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8116,31 +8349,32 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8211,8 +8445,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8306,8 +8543,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8401,8 +8641,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8496,289 +8739,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1060000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-17000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-29000</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-9000</v>
       </c>
       <c r="I100" s="3">
         <v>-9000</v>
       </c>
       <c r="J100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-12000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>189000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>21000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>13000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>118000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-106000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-108000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>349000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-75000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>53000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-23000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>19000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>15000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-102000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>157000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-88000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-28000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="E101" s="3">
-        <v>-5000</v>
+        <v>4000</v>
       </c>
       <c r="F101" s="3">
-        <v>-25000</v>
+        <v>6000</v>
       </c>
       <c r="G101" s="3">
-        <v>-9000</v>
+        <v>4000</v>
       </c>
       <c r="H101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3">
         <v>4000</v>
       </c>
-      <c r="I101" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>4000</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-13000</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>2000</v>
       </c>
       <c r="T101" s="3">
         <v>2000</v>
       </c>
       <c r="U101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="V101" s="3">
         <v>-8000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>2000</v>
       </c>
       <c r="AF101" s="3">
         <v>2000</v>
       </c>
       <c r="AG101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+        <v>2000</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-190000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-33000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>267000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>87000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-33000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>74000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>11000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-535000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>93000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>107000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>71000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>257000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-102000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>24000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>216000</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-10000</v>
       </c>
       <c r="W102" s="3">
         <v>-10000</v>
       </c>
       <c r="X102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-70000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>81000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>91000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>19000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>10000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>REZI</t>
   </si>
@@ -656,439 +656,451 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1858000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1828000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1589000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1486000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1537000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1554000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1602000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1549000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1560000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1618000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1686000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1506000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1454000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1496000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1477000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1419000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1501000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1362000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1029000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1179000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1304000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1226000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1242000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1216000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1266000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1200000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1196000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1165000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1209000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1152000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1096000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1062000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1328000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1304000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1142000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1086000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1114000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1137000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1166000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1131000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1129000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1188000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1219000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1072000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1058000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1080000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1096000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1051000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1076000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>990000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>789000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>892000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>930000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>932000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>933000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>903000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>936000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>853000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>850000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>822000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>848000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>816000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>788000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>751000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>530000</v>
+      </c>
+      <c r="E10" s="3">
         <v>524000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>447000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>400000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>423000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>417000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>436000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>418000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>431000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>430000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>467000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>434000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>396000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>416000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>381000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>368000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>425000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>372000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>240000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>287000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>374000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>294000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>309000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>313000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>330000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>347000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>346000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>343000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>361000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>336000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>308000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>311000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1123,56 +1135,57 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E12" s="3">
         <v>23000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>25000</v>
       </c>
       <c r="G12" s="3">
         <v>25000</v>
       </c>
       <c r="H12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="I12" s="3">
         <v>28000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>30000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>22000</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1221,8 +1234,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1319,88 +1335,91 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E14" s="3">
         <v>74000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>58000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>50000</v>
       </c>
       <c r="G14" s="3">
         <v>50000</v>
       </c>
       <c r="H14" s="3">
+        <v>54000</v>
+      </c>
+      <c r="I14" s="3">
         <v>81000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>46000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>76000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>43000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>45000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>41000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>35000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>57000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>36000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>59000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>13000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>11000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>9000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-17000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>40000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1417,8 +1436,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1426,35 +1448,35 @@
         <v>29000</v>
       </c>
       <c r="E15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F15" s="3">
         <v>13000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>10000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>10000</v>
       </c>
       <c r="L15" s="3">
         <v>10000</v>
       </c>
       <c r="M15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N15" s="3">
         <v>9000</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1470,8 +1492,8 @@
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1515,8 +1537,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1548,204 +1573,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1679000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1673000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1456000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1351000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1381000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1399000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1407000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1447000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1409000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1503000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1506000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1545000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1375000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1348000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1386000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1392000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1348000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1349000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1231000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1035000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1145000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1232000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1167000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1200000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1131000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1208000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1218000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1190000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1188000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1095000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1057000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1015000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E18" s="3">
         <v>155000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>133000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>135000</v>
       </c>
-      <c r="G18" s="3">
-        <v>156000</v>
-      </c>
       <c r="H18" s="3">
+        <v>138000</v>
+      </c>
+      <c r="I18" s="3">
         <v>147000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>155000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>140000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>57000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>112000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>141000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>131000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>106000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>110000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>85000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>71000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>152000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>131000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>34000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>72000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>59000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>42000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>85000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>58000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>78000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>21000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>57000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>39000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1780,91 +1812,92 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E20" s="3">
         <v>10000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-10000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="I20" s="3">
         <v>13000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>40000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>31000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>15000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-41000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-35000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-29000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-42000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-64000</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-35000</v>
       </c>
       <c r="Y20" s="3">
         <v>-35000</v>
       </c>
       <c r="Z20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="AA20" s="3">
         <v>16000</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>1000</v>
       </c>
       <c r="AE20" s="3">
         <v>1000</v>
@@ -1873,189 +1906,195 @@
         <v>1000</v>
       </c>
       <c r="AG20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E21" s="3">
         <v>174000</v>
-      </c>
-      <c r="E21" s="3">
-        <v>145000</v>
       </c>
       <c r="F21" s="3">
         <v>145000</v>
       </c>
       <c r="G21" s="3">
-        <v>176000</v>
+        <v>145000</v>
       </c>
       <c r="H21" s="3">
+        <v>180000</v>
+      </c>
+      <c r="I21" s="3">
         <v>143000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>167000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>109000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>113000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>135000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>170000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>152000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>134000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>131000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>115000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>109000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>133000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>118000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-14000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>13000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>33000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>43000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>27000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>117000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>75000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>21000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>96000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>39000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>75000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>56000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E22" s="3">
         <v>27000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>17000</v>
       </c>
       <c r="J22" s="3">
         <v>17000</v>
       </c>
       <c r="K22" s="3">
+        <v>17000</v>
+      </c>
+      <c r="L22" s="3">
         <v>18000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>11000</v>
       </c>
       <c r="O22" s="3">
         <v>11000</v>
       </c>
       <c r="P22" s="3">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="Q22" s="3">
         <v>12000</v>
       </c>
       <c r="R22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="S22" s="3">
         <v>13000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>14000</v>
       </c>
       <c r="T22" s="3">
         <v>14000</v>
       </c>
       <c r="U22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="V22" s="3">
         <v>18000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>17000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>16000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>18000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>17000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20000</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2074,204 +2113,213 @@
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E23" s="3">
         <v>44000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>59000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>73000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>101000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>37000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>94000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>81000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>70000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>96000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>131000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>121000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>102000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>97000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>81000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>73000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>97000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>82000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-53000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-25000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>84000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>38000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>79000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>22000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>58000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>39000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E24" s="3">
         <v>24000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>29000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>30000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>19000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>44000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>24000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>31000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>33000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>37000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>34000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>35000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>29000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>23000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>24000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>38000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>23000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-4000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1000</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>36000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>339100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-329000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>34000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>18000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>35000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>23000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2368,204 +2416,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E26" s="3">
         <v>20000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>30000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>43000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>82000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>50000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>57000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>39000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>63000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>94000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>87000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>67000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>68000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>58000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>49000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>59000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>75000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-76000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-21000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>8000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>48000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-301100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>311000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>30000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>45000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>23000</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>16000</v>
       </c>
       <c r="AH26" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E27" s="3">
         <v>11000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>25000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>43000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>82000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>50000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>57000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>39000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>63000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>94000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>87000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>67000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>68000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>58000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>49000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>59000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>75000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-76000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-21000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>48000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-301100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>311000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>30000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>45000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>23000</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>16000</v>
       </c>
       <c r="AH27" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2662,8 +2719,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2718,8 +2778,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2736,32 +2796,35 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>317100</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>3000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-453000</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2858,8 +2921,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2956,91 +3022,94 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
-        <v>10000</v>
-      </c>
       <c r="H32" s="3">
+        <v>32000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-13000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-40000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-31000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-15000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>41000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>35000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>29000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>42000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>64000</v>
-      </c>
-      <c r="X32" s="3">
-        <v>35000</v>
       </c>
       <c r="Y32" s="3">
         <v>35000</v>
       </c>
       <c r="Z32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AE32" s="3">
         <v>-1000</v>
@@ -3049,111 +3118,117 @@
         <v>-1000</v>
       </c>
       <c r="AG32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E33" s="3">
         <v>20000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>30000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>43000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>82000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>50000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>57000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>39000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>63000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>94000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>87000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>67000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>68000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>58000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>49000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>59000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>75000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-76000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-21000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>48000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>16000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>311000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>33000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>45000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-449000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>23000</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>16000</v>
       </c>
       <c r="AH33" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3250,209 +3325,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E35" s="3">
         <v>20000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>30000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>43000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>82000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>50000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>57000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>39000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>63000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>94000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>87000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>67000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>68000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>58000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>49000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>59000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>75000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-76000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-21000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>48000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>16000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>311000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>33000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>45000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-449000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>23000</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>16000</v>
       </c>
       <c r="AH35" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,8 +3571,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3523,95 +3608,96 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>692000</v>
+      </c>
+      <c r="E41" s="3">
         <v>531000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>413000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>603000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>636000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>368000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>381000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>292000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>326000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>252000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>251000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>244000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>779000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>686000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>579000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>508000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>517000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>260000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>362000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>338000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>122000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>132000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>142000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>212000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>265000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>184000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>93000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>75000</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3621,35 +3707,38 @@
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E42" s="3">
         <v>13000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19000</v>
-      </c>
-      <c r="F42" s="3">
-        <v>20000</v>
       </c>
       <c r="G42" s="3">
         <v>20000</v>
       </c>
       <c r="H42" s="3">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="I42" s="3">
         <v>23000</v>
       </c>
       <c r="J42" s="3">
+        <v>23000</v>
+      </c>
+      <c r="K42" s="3">
         <v>21000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3719,95 +3808,98 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1023000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1103000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1071000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>933000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>973000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>988000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1043000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>985000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1002000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1043000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1073000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1008000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>876000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>932000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>895000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>875000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>863000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>884000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>704000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>820000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>817000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>845000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>835000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>838000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>821000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>809000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>766000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>756000</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3817,95 +3909,98 @@
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1237000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1197000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1188000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>929000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>941000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>970000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1001000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1008000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>975000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>957000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>971000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>922000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>740000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>710000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>684000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>681000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>672000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>618000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>614000</v>
-      </c>
-      <c r="V44" s="3">
-        <v>671000</v>
       </c>
       <c r="W44" s="3">
         <v>671000</v>
       </c>
       <c r="X44" s="3">
+        <v>671000</v>
+      </c>
+      <c r="Y44" s="3">
         <v>729000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>722000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>701000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>628000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>603000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>523000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>481000</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3915,95 +4010,98 @@
       <c r="AH44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>193000</v>
+        <v>210000</v>
       </c>
       <c r="E45" s="3">
         <v>193000</v>
       </c>
       <c r="F45" s="3">
+        <v>193000</v>
+      </c>
+      <c r="G45" s="3">
         <v>192000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>173000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>266000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>174000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>189000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>199000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>198000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>186000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>165000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>146000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>179000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>198000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>156000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>173000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>161000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>163000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>164000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>175000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>134000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>147000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>111000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>95000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>72000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>74000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>65000</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4013,95 +4111,98 @@
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3172000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3037000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2884000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2677000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2743000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2615000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2622000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2495000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2502000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2450000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2481000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2339000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2541000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2507000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2356000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2220000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2225000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1923000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1843000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1993000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1785000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1840000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1846000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1862000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1809000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1668000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1456000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1377000</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4111,35 +4212,38 @@
       <c r="AH46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>10000</v>
       </c>
       <c r="G47" s="3">
         <v>10000</v>
       </c>
       <c r="H47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I47" s="3">
         <v>18000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>17000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4209,95 +4313,98 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>658000</v>
+      </c>
+      <c r="E48" s="3">
         <v>648000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>658000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>552000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>582000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>577000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>580000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>571000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>557000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>538000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>535000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>514000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>428000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>424000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>438000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>442000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>451000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>445000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>440000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>433000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>453000</v>
-      </c>
-      <c r="X48" s="3">
-        <v>436000</v>
       </c>
       <c r="Y48" s="3">
         <v>436000</v>
       </c>
       <c r="Z48" s="3">
+        <v>436000</v>
+      </c>
+      <c r="AA48" s="3">
         <v>413000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>300000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>276000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>264000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>267000</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4307,95 +4414,98 @@
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4248000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4316000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4297000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3145000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3166000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3143000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3204000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3207000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3199000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3138000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3158000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3125000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2661000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2671000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2682000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2675000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2691000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2657000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2638000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2612000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2769000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2757000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2777000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2772000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2767000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2776000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2766000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2810000</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4405,8 +4515,11 @@
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4503,8 +4616,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4601,95 +4717,98 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E52" s="3">
         <v>132000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>137000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>136000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>144000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>106000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>110000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>109000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>129000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>136000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>142000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>267000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>223000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>232000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>236000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>239000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>243000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>244000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>245000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>249000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>121000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>100000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>101000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>97000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>96000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>22000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>21000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>28000</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4699,8 +4818,11 @@
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4797,95 +4919,98 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8199000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8135000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7984000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6520000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6645000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6459000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6536000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6399000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6387000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6262000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6316000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6245000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5853000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5834000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5712000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5576000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5610000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5269000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5166000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5287000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5128000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5133000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5160000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5144000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4972000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4742000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4507000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4482000</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4895,8 +5020,11 @@
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4931,8 +5059,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4967,95 +5096,96 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1073000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1021000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>980000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>858000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>905000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>863000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>948000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>894000</v>
       </c>
       <c r="K57" s="3">
         <v>894000</v>
       </c>
       <c r="L57" s="3">
+        <v>894000</v>
+      </c>
+      <c r="M57" s="3">
         <v>936000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>987000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>958000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>883000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>905000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>915000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>908000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>936000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>858000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>811000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>906000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>920000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>932000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1009000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1013000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>964000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>850000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>774000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>712000</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5065,34 +5195,37 @@
       <c r="AH57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E58" s="3">
         <v>56000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>64000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>50000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>51000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>48000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>50000</v>
       </c>
       <c r="J58" s="3">
         <v>50000</v>
       </c>
       <c r="K58" s="3">
-        <v>12000</v>
+        <v>50000</v>
       </c>
       <c r="L58" s="3">
         <v>12000</v>
@@ -5104,7 +5237,7 @@
         <v>12000</v>
       </c>
       <c r="O58" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="P58" s="3">
         <v>10000</v>
@@ -5116,25 +5249,25 @@
         <v>10000</v>
       </c>
       <c r="S58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="T58" s="3">
         <v>7000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>181000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>287000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>382000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>22000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>88000</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>22000</v>
       </c>
       <c r="Z58" s="3">
         <v>22000</v>
@@ -5142,8 +5275,8 @@
       <c r="AA58" s="3">
         <v>22000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
+      <c r="AB58" s="3">
+        <v>22000</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
@@ -5163,95 +5296,98 @@
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E59" s="3">
         <v>236000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>196000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>216000</v>
       </c>
-      <c r="G59" s="3">
-        <v>228000</v>
-      </c>
       <c r="H59" s="3">
-        <v>212000</v>
+        <v>232000</v>
       </c>
       <c r="I59" s="3">
+        <v>253000</v>
+      </c>
+      <c r="J59" s="3">
         <v>198000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>210000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>640000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>594000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>580000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>576000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>601000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>617000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>586000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>528000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>595000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>606000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>564000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>467000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>552000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>531000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>528000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>524000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>503000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>550000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>459000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>418000</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5261,95 +5397,98 @@
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1790000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1672000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1594000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1385000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1525000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1467000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1524000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1469000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1546000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1542000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1579000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1546000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1494000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1532000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1511000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1446000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1538000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1645000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1662000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1755000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1494000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1551000</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>1559000</v>
       </c>
       <c r="Z60" s="3">
         <v>1559000</v>
       </c>
       <c r="AA60" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="AB60" s="3">
         <v>1489000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1400000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1233000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1130000</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5359,86 +5498,89 @@
       <c r="AH60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2195000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2177000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2181000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1553000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1562000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1571000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1566000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1568000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1404000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1407000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1410000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1412000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1220000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1222000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1184000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1186000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1155000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1006000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1011000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1149000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1158000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1165000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1169000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1174000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1179000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5457,95 +5599,98 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>805000</v>
+      </c>
+      <c r="E62" s="3">
         <v>932000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>915000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>813000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>692000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>776000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>769000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>758000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>908000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>913000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>933000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>926000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>887000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>922000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>914000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>912000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>924000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1013000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>998000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>862000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>874000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>844000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>839000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>819000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>771000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>657000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>794000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>763000</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5555,8 +5700,11 @@
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5653,8 +5801,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5751,8 +5902,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5849,95 +6003,98 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4890000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4781000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4690000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3751000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3896000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3814000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3859000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3795000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3858000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3862000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3922000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3884000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3601000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3676000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3609000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3544000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3617000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3664000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3671000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3766000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3526000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3560000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3567000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3552000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3439000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2057000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2027000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1893000</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5947,8 +6104,11 @@
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5983,8 +6143,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6081,8 +6242,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6179,8 +6343,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6191,7 +6358,7 @@
         <v>482000</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>482000</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -6277,8 +6444,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6375,86 +6545,89 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>907000</v>
+      </c>
+      <c r="E72" s="3">
         <v>893000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>881000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>853000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>810000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>728000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>707000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>657000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>600000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>561000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>498000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>404000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>317000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>250000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>182000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>124000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>75000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-59000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>17000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>47000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>39000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>50000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6473,8 +6646,11 @@
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6571,8 +6747,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6669,8 +6848,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6767,95 +6949,98 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2827000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2872000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2812000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2769000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2749000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2645000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2677000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2604000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2529000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2400000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2394000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2361000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2252000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2158000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2103000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2032000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1993000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1605000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1495000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1521000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1602000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1573000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1593000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1592000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1533000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2685000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2480000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2589000</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6865,8 +7050,11 @@
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6963,209 +7151,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E81" s="3">
         <v>20000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>30000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>43000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>82000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>50000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>57000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>39000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>63000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>94000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>87000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>67000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>68000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>58000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>49000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>59000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>75000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-76000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-21000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>48000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>16000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>311000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>33000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>45000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-449000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>23000</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>16000</v>
       </c>
       <c r="AH81" s="3">
         <v>16000</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7200,94 +7397,95 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E83" s="3">
         <v>13000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>15000</v>
       </c>
       <c r="H83" s="3">
         <v>15000</v>
       </c>
       <c r="I83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J83" s="3">
         <v>9000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>21000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>22000</v>
       </c>
       <c r="Q83" s="3">
         <v>22000</v>
       </c>
       <c r="R83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="S83" s="3">
         <v>23000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>22000</v>
       </c>
       <c r="T83" s="3">
         <v>22000</v>
       </c>
       <c r="U83" s="3">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="V83" s="3">
         <v>21000</v>
       </c>
       <c r="W83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="X83" s="3">
         <v>25000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>19000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>16000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>17000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>16000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>13000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>20000</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>17000</v>
       </c>
       <c r="AF83" s="3">
         <v>17000</v>
@@ -7296,10 +7494,13 @@
         <v>17000</v>
       </c>
       <c r="AH83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AI83" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7396,8 +7597,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7494,8 +7698,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7592,8 +7799,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7690,8 +7900,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7788,106 +8001,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>203000</v>
+      </c>
+      <c r="E89" s="3">
         <v>147000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>92000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>263000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>60000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>121000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>139000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>37000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>35000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-59000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>112000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>104000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>94000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>152000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>145000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-74000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>93000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-33000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>87000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>117000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>132000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>126000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-143000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>111000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>30000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7922,8 +8141,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7931,97 +8151,100 @@
         <v>-22000</v>
       </c>
       <c r="E91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-15000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-21000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-29000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-51000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-29000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-23000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8118,8 +8341,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8216,106 +8442,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1342000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>46000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-35000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-57000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-37000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-665000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-24000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-18000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-51000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-29000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-34000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-39000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8350,8 +8582,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8376,8 +8609,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8448,8 +8681,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8546,8 +8782,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8644,8 +8883,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8742,298 +8984,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1060000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-17000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-29000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-9000</v>
       </c>
       <c r="J100" s="3">
         <v>-9000</v>
       </c>
       <c r="K100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="L100" s="3">
         <v>-12000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>189000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>21000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>13000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>118000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-106000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-108000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>349000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-75000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>53000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-23000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>19000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>15000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-102000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>157000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-88000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-28000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-13000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3">
         <v>4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-13000</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>5000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>2000</v>
       </c>
       <c r="U101" s="3">
         <v>2000</v>
       </c>
       <c r="V101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W101" s="3">
         <v>-8000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>2000</v>
       </c>
       <c r="AG101" s="3">
         <v>2000</v>
       </c>
       <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+        <v>2000</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E102" s="3">
         <v>118000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-190000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-33000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>267000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>87000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-33000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>74000</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>11000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-535000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>93000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>107000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>71000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>257000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-102000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>24000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>216000</v>
-      </c>
-      <c r="W102" s="3">
-        <v>-10000</v>
       </c>
       <c r="X102" s="3">
         <v>-10000</v>
       </c>
       <c r="Y102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-70000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>81000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>91000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>19000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>10000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>REZI</t>
   </si>
@@ -656,451 +656,464 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1770000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1858000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1828000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1589000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1486000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1537000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1554000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1602000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1549000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1560000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1618000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1686000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1506000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1454000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1496000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1477000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1419000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1501000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1362000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1029000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1179000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1304000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1226000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1242000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1216000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1266000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1200000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1196000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1165000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1209000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1152000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1096000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1062000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1259000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1328000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1304000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1142000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1086000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1114000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1137000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1166000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1131000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1129000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1188000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1219000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1072000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1058000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1080000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1096000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1051000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1076000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>990000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>789000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>892000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>930000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>932000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>933000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>903000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>936000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>853000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>850000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>822000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>848000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>816000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>788000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>751000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E10" s="3">
         <v>530000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>524000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>447000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>400000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>423000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>417000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>436000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>418000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>431000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>430000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>467000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>434000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>396000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>416000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>381000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>368000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>425000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>372000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>240000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>287000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>374000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>294000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>309000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>313000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>330000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>347000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>346000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>343000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>361000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>336000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>308000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>311000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1136,59 +1149,60 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E12" s="3">
         <v>42000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>25000</v>
       </c>
       <c r="H12" s="3">
         <v>25000</v>
       </c>
       <c r="I12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J12" s="3">
         <v>28000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>30000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>28000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>22000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1237,8 +1251,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1338,91 +1355,94 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E14" s="3">
         <v>115000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>74000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>58000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>50000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>54000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>81000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>46000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>76000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>43000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>45000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>41000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>35000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>57000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>36000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>59000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>13000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>11000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>9000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-17000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>40000</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1439,47 +1459,50 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>29000</v>
+        <v>30000</v>
       </c>
       <c r="E15" s="3">
         <v>29000</v>
       </c>
       <c r="F15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="G15" s="3">
         <v>13000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>10000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>10000</v>
       </c>
       <c r="M15" s="3">
         <v>10000</v>
       </c>
       <c r="N15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O15" s="3">
         <v>9000</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1495,8 +1518,8 @@
       <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1540,8 +1563,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1574,210 +1600,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1630000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1679000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1673000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1456000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1351000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1399000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1407000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1447000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1409000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1503000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1506000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1545000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1375000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1348000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1386000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1392000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1348000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1349000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1231000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1035000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1145000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1232000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1167000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1200000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1131000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1208000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1218000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1190000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1188000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1095000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1057000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1015000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E18" s="3">
         <v>179000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>155000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>133000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>135000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>138000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>147000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>155000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>140000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>57000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>112000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>141000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>131000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>106000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>110000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>85000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>71000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>152000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>131000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>34000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>72000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>59000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>42000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>85000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>58000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>78000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>21000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>57000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>39000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1813,94 +1846,95 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-32000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>13000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>40000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>31000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>15000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-41000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-35000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-29000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-42000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-64000</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-35000</v>
       </c>
       <c r="Z20" s="3">
         <v>-35000</v>
       </c>
       <c r="AA20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>16000</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>1000</v>
       </c>
       <c r="AF20" s="3">
         <v>1000</v>
@@ -1909,195 +1943,201 @@
         <v>1000</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E21" s="3">
         <v>215000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>174000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>145000</v>
       </c>
       <c r="G21" s="3">
         <v>145000</v>
       </c>
       <c r="H21" s="3">
+        <v>145000</v>
+      </c>
+      <c r="I21" s="3">
         <v>180000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>143000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>167000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>109000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>113000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>135000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>170000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>152000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>134000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>131000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>115000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>109000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>133000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>118000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-14000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>13000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>33000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>43000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>27000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>117000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>75000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>21000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>96000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>39000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>75000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>56000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E22" s="3">
         <v>26000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>15000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>17000</v>
       </c>
       <c r="K22" s="3">
         <v>17000</v>
       </c>
       <c r="L22" s="3">
+        <v>17000</v>
+      </c>
+      <c r="M22" s="3">
         <v>18000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>11000</v>
       </c>
       <c r="P22" s="3">
         <v>11000</v>
       </c>
       <c r="Q22" s="3">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="R22" s="3">
         <v>12000</v>
       </c>
       <c r="S22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="T22" s="3">
         <v>13000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>14000</v>
       </c>
       <c r="U22" s="3">
         <v>14000</v>
       </c>
       <c r="V22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="W22" s="3">
         <v>18000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>17000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>18000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>16000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>18000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>17000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20000</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2116,210 +2156,219 @@
       <c r="AI22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E23" s="3">
         <v>45000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>44000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>59000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>73000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>101000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>37000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>94000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>81000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>70000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>96000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>131000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>121000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>102000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>97000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>81000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>73000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>97000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>82000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-53000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-25000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>84000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>38000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>79000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>22000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>58000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>39000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E24" s="3">
         <v>22000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>24000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>29000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>30000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>19000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>16000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>44000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>24000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>31000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>33000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>37000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>34000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>35000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>29000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>23000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>24000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>38000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>23000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-4000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>36000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>339100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-329000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>34000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>18000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>35000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>23000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2419,210 +2468,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E26" s="3">
         <v>23000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>20000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>30000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>43000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>82000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>50000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>57000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>39000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>63000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>94000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>87000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>67000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>68000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>58000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>49000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>59000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>75000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-76000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-21000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>8000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>48000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-301100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>311000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>30000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>45000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>23000</v>
-      </c>
-      <c r="AH26" s="3">
-        <v>16000</v>
       </c>
       <c r="AI26" s="3">
         <v>16000</v>
       </c>
+      <c r="AJ26" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>12000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>25000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>43000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>82000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>50000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>57000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>39000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>63000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>94000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>87000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>67000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>68000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>58000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>49000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>59000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>75000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-76000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-21000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>8000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>48000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-301100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>311000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>30000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>45000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>23000</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>16000</v>
       </c>
       <c r="AI27" s="3">
         <v>16000</v>
       </c>
+      <c r="AJ27" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2722,8 +2780,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2781,8 +2842,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2799,32 +2860,35 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>317100</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>3000</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-453000</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2924,8 +2988,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3025,94 +3092,97 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>7000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>32000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-13000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-40000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-31000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-15000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>41000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>35000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>29000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>42000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>64000</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>35000</v>
       </c>
       <c r="Z32" s="3">
         <v>35000</v>
       </c>
       <c r="AA32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>1000</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AF32" s="3">
         <v>-1000</v>
@@ -3121,114 +3191,120 @@
         <v>-1000</v>
       </c>
       <c r="AH32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E33" s="3">
         <v>23000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>30000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>43000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>82000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>50000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>57000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>39000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>63000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>94000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>87000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>67000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>68000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>58000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>49000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>59000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>75000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-76000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-21000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>8000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>48000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>16000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>311000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>33000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>45000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-449000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>23000</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>16000</v>
       </c>
       <c r="AI33" s="3">
         <v>16000</v>
       </c>
+      <c r="AJ33" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3328,215 +3404,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E35" s="3">
         <v>23000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>30000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>43000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>82000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>50000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>57000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>39000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>63000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>94000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>87000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>67000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>68000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>58000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>49000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>59000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>75000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-76000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-21000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>8000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>48000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>16000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>311000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>33000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>45000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-449000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>23000</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>16000</v>
       </c>
       <c r="AI35" s="3">
         <v>16000</v>
       </c>
+      <c r="AJ35" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3572,8 +3657,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3609,98 +3695,99 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>577000</v>
+      </c>
+      <c r="E41" s="3">
         <v>692000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>531000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>413000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>603000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>636000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>368000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>381000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>292000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>326000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>252000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>251000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>244000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>779000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>686000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>579000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>508000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>517000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>260000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>362000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>338000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>122000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>132000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>142000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>212000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>265000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>184000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>93000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>75000</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3710,38 +3797,41 @@
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E42" s="3">
         <v>10000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19000</v>
-      </c>
-      <c r="G42" s="3">
-        <v>20000</v>
       </c>
       <c r="H42" s="3">
         <v>20000</v>
       </c>
       <c r="I42" s="3">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="J42" s="3">
         <v>23000</v>
       </c>
       <c r="K42" s="3">
+        <v>23000</v>
+      </c>
+      <c r="L42" s="3">
         <v>21000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3811,98 +3901,101 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1045000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1023000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1103000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1071000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>933000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>973000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>988000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1043000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>985000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1002000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1043000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1073000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1008000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>876000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>932000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>895000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>875000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>863000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>884000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>704000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>820000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>817000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>845000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>835000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>838000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>821000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>809000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>766000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>756000</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3912,98 +4005,101 @@
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1228000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1237000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1197000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1188000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>929000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>941000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>970000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1001000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1008000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>975000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>957000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>971000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>922000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>740000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>710000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>684000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>681000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>672000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>618000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>614000</v>
-      </c>
-      <c r="W44" s="3">
-        <v>671000</v>
       </c>
       <c r="X44" s="3">
         <v>671000</v>
       </c>
       <c r="Y44" s="3">
+        <v>671000</v>
+      </c>
+      <c r="Z44" s="3">
         <v>729000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>722000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>701000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>628000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>603000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>523000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>481000</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4013,98 +4109,101 @@
       <c r="AI44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E45" s="3">
         <v>210000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>193000</v>
       </c>
       <c r="F45" s="3">
         <v>193000</v>
       </c>
       <c r="G45" s="3">
+        <v>193000</v>
+      </c>
+      <c r="H45" s="3">
         <v>192000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>173000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>266000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>174000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>189000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>199000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>198000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>186000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>165000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>146000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>179000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>198000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>156000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>173000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>161000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>163000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>164000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>175000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>134000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>147000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>111000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>95000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>72000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>74000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>65000</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4114,98 +4213,101 @@
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3061000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3172000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3037000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2884000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2677000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2743000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2615000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2622000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2495000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2502000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2450000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2481000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2339000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2541000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2507000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2356000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2220000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2225000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1923000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1843000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1993000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1785000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1840000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1846000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1862000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1809000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1668000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1456000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1377000</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4215,38 +4317,41 @@
       <c r="AI46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>10000</v>
       </c>
       <c r="H47" s="3">
         <v>10000</v>
       </c>
       <c r="I47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J47" s="3">
         <v>18000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>17000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4316,98 +4421,101 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>652000</v>
+      </c>
+      <c r="E48" s="3">
         <v>658000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>648000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>658000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>552000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>582000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>577000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>580000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>571000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>557000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>538000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>535000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>514000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>428000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>424000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>438000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>442000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>451000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>445000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>440000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>433000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>453000</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>436000</v>
       </c>
       <c r="Z48" s="3">
         <v>436000</v>
       </c>
       <c r="AA48" s="3">
+        <v>436000</v>
+      </c>
+      <c r="AB48" s="3">
         <v>413000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>300000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>276000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>264000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>267000</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4417,98 +4525,101 @@
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4241000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4248000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4316000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4297000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3145000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3166000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3143000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3204000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3207000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3199000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3138000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3158000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3125000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2661000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2671000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2682000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2675000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2691000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2657000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2638000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2612000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2769000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2757000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2777000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2772000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2767000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2776000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2766000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2810000</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4518,8 +4629,11 @@
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4619,8 +4733,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4720,8 +4837,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4729,89 +4849,89 @@
         <v>118000</v>
       </c>
       <c r="E52" s="3">
+        <v>118000</v>
+      </c>
+      <c r="F52" s="3">
         <v>132000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>137000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>136000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>144000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>106000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>110000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>109000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>129000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>136000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>142000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>267000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>223000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>232000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>236000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>239000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>243000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>244000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>245000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>249000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>121000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>100000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>101000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>97000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>96000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>22000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>21000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>28000</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4821,8 +4941,11 @@
       <c r="AI52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4922,98 +5045,101 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8074000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8199000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8135000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7984000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6520000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6645000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6459000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6536000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6399000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6387000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6262000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6316000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6245000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5853000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5834000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5712000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5576000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5610000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5269000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5166000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5287000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5128000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5133000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5160000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5144000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4972000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4742000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4507000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4482000</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5023,8 +5149,11 @@
       <c r="AI54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5060,8 +5189,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5097,98 +5227,99 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>971000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1073000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1021000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>980000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>858000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>905000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>863000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>948000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>894000</v>
       </c>
       <c r="L57" s="3">
         <v>894000</v>
       </c>
       <c r="M57" s="3">
+        <v>894000</v>
+      </c>
+      <c r="N57" s="3">
         <v>936000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>987000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>958000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>883000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>905000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>915000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>908000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>936000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>858000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>811000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>906000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>920000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>932000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1009000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1013000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>964000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>850000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>774000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>712000</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5198,37 +5329,40 @@
       <c r="AI57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E58" s="3">
         <v>57000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>56000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>64000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>50000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>51000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>48000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>50000</v>
       </c>
       <c r="K58" s="3">
         <v>50000</v>
       </c>
       <c r="L58" s="3">
-        <v>12000</v>
+        <v>50000</v>
       </c>
       <c r="M58" s="3">
         <v>12000</v>
@@ -5240,7 +5374,7 @@
         <v>12000</v>
       </c>
       <c r="P58" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="Q58" s="3">
         <v>10000</v>
@@ -5252,25 +5386,25 @@
         <v>10000</v>
       </c>
       <c r="T58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="U58" s="3">
         <v>7000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>181000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>287000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>382000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>22000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>88000</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>22000</v>
       </c>
       <c r="AA58" s="3">
         <v>22000</v>
@@ -5278,8 +5412,8 @@
       <c r="AB58" s="3">
         <v>22000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
+      <c r="AC58" s="3">
+        <v>22000</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
@@ -5299,98 +5433,101 @@
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>238000</v>
+      </c>
+      <c r="E59" s="3">
         <v>262000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>236000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>196000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>216000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>232000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>253000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>198000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>210000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>640000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>594000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>580000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>576000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>601000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>617000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>586000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>528000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>595000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>606000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>564000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>467000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>552000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>531000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>528000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>524000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>503000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>550000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>459000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>418000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5400,98 +5537,101 @@
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1578000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1790000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1672000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1594000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1385000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1525000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1467000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1524000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1469000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1546000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1542000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1579000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1546000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1494000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1532000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1511000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1446000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1538000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1645000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1662000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1755000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1494000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1551000</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>1559000</v>
       </c>
       <c r="AA60" s="3">
         <v>1559000</v>
       </c>
       <c r="AB60" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="AC60" s="3">
         <v>1489000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1400000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1233000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1130000</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5501,89 +5641,92 @@
       <c r="AI60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2190000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2195000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2177000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2181000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1553000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1562000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1571000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1566000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1568000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1404000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1407000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1410000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1412000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1220000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1222000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1184000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1186000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1155000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1006000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1011000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1149000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1158000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1165000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1169000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1174000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1179000</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5602,98 +5745,101 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>959000</v>
+      </c>
+      <c r="E62" s="3">
         <v>805000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>932000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>915000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>813000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>692000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>776000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>769000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>758000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>908000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>913000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>933000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>926000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>887000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>922000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>914000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>912000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>924000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1013000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>998000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>862000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>874000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>844000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>839000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>819000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>771000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>657000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>794000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>763000</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5703,8 +5849,11 @@
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5804,8 +5953,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5905,8 +6057,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6006,98 +6161,101 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4727000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4890000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4781000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4690000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3751000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3896000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3814000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3859000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3795000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3858000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3862000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3922000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3884000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3601000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3676000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3609000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3544000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3617000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3664000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3671000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3766000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3526000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3560000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3567000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3552000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3439000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2057000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2027000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1893000</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6107,8 +6265,11 @@
       <c r="AI66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6144,8 +6305,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6245,8 +6407,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6346,8 +6511,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6361,7 +6529,7 @@
         <v>482000</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>482000</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -6447,8 +6615,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6548,89 +6719,92 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>904000</v>
+      </c>
+      <c r="E72" s="3">
         <v>907000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>893000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>881000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>853000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>810000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>728000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>707000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>657000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>600000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>561000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>498000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>404000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>317000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>250000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>182000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>124000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>75000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>16000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-59000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>17000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>38000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>39000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>50000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2000</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6649,8 +6823,11 @@
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6750,8 +6927,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6851,8 +7031,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6952,98 +7135,101 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2865000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2827000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2872000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2812000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2769000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2749000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2645000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2677000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2604000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2529000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2400000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2394000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2361000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2252000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2158000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2103000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2032000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1993000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1605000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1495000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1521000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1602000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1573000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1593000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1592000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1533000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2685000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2480000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2589000</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7053,8 +7239,11 @@
       <c r="AI76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7154,215 +7343,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E81" s="3">
         <v>23000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>30000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>43000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>82000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>50000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>57000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>39000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>63000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>94000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>87000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>67000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>68000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>58000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>49000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>59000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>75000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-76000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-21000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>8000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>48000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>16000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>311000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>33000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>45000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-449000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>23000</v>
-      </c>
-      <c r="AH81" s="3">
-        <v>16000</v>
       </c>
       <c r="AI81" s="3">
         <v>16000</v>
       </c>
+      <c r="AJ81" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7398,97 +7596,98 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E83" s="3">
         <v>17000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>15000</v>
       </c>
       <c r="I83" s="3">
         <v>15000</v>
       </c>
       <c r="J83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K83" s="3">
         <v>9000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>25000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>21000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>22000</v>
       </c>
       <c r="R83" s="3">
         <v>22000</v>
       </c>
       <c r="S83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="T83" s="3">
         <v>23000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>22000</v>
       </c>
       <c r="U83" s="3">
         <v>22000</v>
       </c>
       <c r="V83" s="3">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="W83" s="3">
         <v>21000</v>
       </c>
       <c r="X83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="Y83" s="3">
         <v>25000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>19000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>16000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>17000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>16000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>13000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>20000</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>17000</v>
       </c>
       <c r="AG83" s="3">
         <v>17000</v>
@@ -7497,10 +7696,13 @@
         <v>17000</v>
       </c>
       <c r="AI83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7600,8 +7802,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7701,8 +7906,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7802,8 +8010,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7903,8 +8114,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8004,109 +8218,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-65000</v>
+      </c>
+      <c r="E89" s="3">
         <v>203000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>147000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>92000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>263000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>60000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>121000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>139000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>37000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>35000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-59000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>112000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>104000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>94000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>152000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>145000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-74000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>93000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-33000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-27000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>87000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>117000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>132000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>126000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-143000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>111000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>30000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8142,109 +8362,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-22000</v>
+        <v>-31000</v>
       </c>
       <c r="E91" s="3">
         <v>-22000</v>
       </c>
       <c r="F91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-15000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-21000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-31000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-29000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-51000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-16000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-23000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8344,8 +8568,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8445,109 +8672,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1342000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>46000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-35000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-57000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-37000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-665000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-24000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-18000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-51000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-34000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-39000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8583,8 +8816,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8612,8 +8846,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8684,8 +8918,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8785,8 +9022,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8886,8 +9126,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8987,307 +9230,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1060000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-29000</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-9000</v>
       </c>
       <c r="K100" s="3">
         <v>-9000</v>
       </c>
       <c r="L100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="M100" s="3">
         <v>-12000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>189000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>21000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>13000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>118000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-106000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-108000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>349000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-75000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>53000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-23000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>19000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>15000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-102000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>157000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-88000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-28000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-25000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3">
         <v>4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13000</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>2000</v>
       </c>
       <c r="V101" s="3">
         <v>2000</v>
       </c>
       <c r="W101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X101" s="3">
         <v>-8000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>2000</v>
       </c>
       <c r="AH101" s="3">
         <v>2000</v>
       </c>
       <c r="AI101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-115000</v>
+      </c>
+      <c r="E102" s="3">
         <v>161000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>118000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-190000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>267000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>87000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-33000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>74000</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>11000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-535000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>93000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>107000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>71000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>257000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-102000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>24000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>216000</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-10000</v>
       </c>
       <c r="Y102" s="3">
         <v>-10000</v>
       </c>
       <c r="Z102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-70000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>81000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>91000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>18000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>19000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>10000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>REZI</t>
   </si>
@@ -656,464 +656,477 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1943000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1770000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1858000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1828000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1589000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1486000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1537000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1554000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1602000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1549000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1560000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1618000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1686000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1506000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1454000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1496000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1477000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1419000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1501000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1362000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1029000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1179000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1304000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1226000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1242000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1216000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1266000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1200000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1196000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1165000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1209000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1152000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1096000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1062000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1259000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1328000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1304000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1142000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1086000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1114000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1137000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1166000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1131000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1129000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1188000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1219000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1072000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1058000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1080000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1096000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1051000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1076000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>990000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>789000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>892000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>930000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>932000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>933000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>903000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>936000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>853000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>850000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>822000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>848000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>816000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>788000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>751000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>569000</v>
+      </c>
+      <c r="E10" s="3">
         <v>511000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>530000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>524000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>447000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>400000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>423000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>417000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>436000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>418000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>431000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>430000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>467000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>434000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>396000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>416000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>381000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>368000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>425000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>372000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>240000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>287000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>374000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>294000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>309000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>313000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>330000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>347000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>346000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>343000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>361000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>336000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>308000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>311000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1150,62 +1163,63 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E12" s="3">
         <v>35000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>42000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>25000</v>
       </c>
       <c r="I12" s="3">
         <v>25000</v>
       </c>
       <c r="J12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="K12" s="3">
         <v>28000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>30000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>23000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>22000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1254,8 +1268,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1358,94 +1375,97 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E14" s="3">
         <v>94000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>115000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>74000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>58000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>50000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>54000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>81000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>46000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>76000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>43000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>45000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>41000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>35000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>57000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>36000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>59000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>13000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>7000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>11000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>9000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-17000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>10000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>40000</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1462,8 +1482,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1471,41 +1494,41 @@
         <v>30000</v>
       </c>
       <c r="E15" s="3">
-        <v>29000</v>
+        <v>30000</v>
       </c>
       <c r="F15" s="3">
         <v>29000</v>
       </c>
       <c r="G15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="H15" s="3">
         <v>13000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>10000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>10000</v>
       </c>
       <c r="N15" s="3">
         <v>10000</v>
       </c>
       <c r="O15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="P15" s="3">
         <v>9000</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1521,8 +1544,8 @@
       <c r="U15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1566,8 +1589,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1601,216 +1627,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1764000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1630000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1679000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1673000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1456000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1351000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1399000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1407000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1447000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1409000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1503000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1506000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1545000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1375000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1348000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1386000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1392000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1348000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1349000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1231000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1035000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1145000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1232000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1167000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1200000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1131000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1208000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1218000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1190000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1188000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1095000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1057000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1015000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E18" s="3">
         <v>140000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>179000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>155000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>133000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>135000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>138000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>147000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>155000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>140000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>57000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>112000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>141000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>131000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>106000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>110000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>85000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>71000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>152000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>131000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>34000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>72000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>59000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>42000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>85000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>58000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>78000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>21000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>57000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1847,97 +1880,98 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E20" s="3">
         <v>6000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-32000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>13000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>40000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>31000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>15000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-41000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-35000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-29000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-64000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-35000</v>
       </c>
       <c r="AA20" s="3">
         <v>-35000</v>
       </c>
       <c r="AB20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>16000</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>1000</v>
       </c>
       <c r="AG20" s="3">
         <v>1000</v>
@@ -1946,201 +1980,207 @@
         <v>1000</v>
       </c>
       <c r="AI20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E21" s="3">
         <v>164000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>215000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>174000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>145000</v>
       </c>
       <c r="H21" s="3">
         <v>145000</v>
       </c>
       <c r="I21" s="3">
+        <v>145000</v>
+      </c>
+      <c r="J21" s="3">
         <v>180000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>143000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>167000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>109000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>113000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>135000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>170000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>152000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>134000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>131000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>115000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>109000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>133000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>118000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-14000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>13000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>33000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>43000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>27000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>117000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>75000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>21000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>96000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>39000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>75000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>56000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E22" s="3">
         <v>25000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>26000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>17000</v>
       </c>
       <c r="L22" s="3">
         <v>17000</v>
       </c>
       <c r="M22" s="3">
+        <v>17000</v>
+      </c>
+      <c r="N22" s="3">
         <v>18000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>11000</v>
       </c>
       <c r="Q22" s="3">
         <v>11000</v>
       </c>
       <c r="R22" s="3">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="S22" s="3">
         <v>12000</v>
       </c>
       <c r="T22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="U22" s="3">
         <v>13000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>14000</v>
       </c>
       <c r="V22" s="3">
         <v>14000</v>
       </c>
       <c r="W22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="X22" s="3">
         <v>18000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>17000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>18000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>18000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>17000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20000</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2159,216 +2199,225 @@
       <c r="AJ22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-738000</v>
+      </c>
+      <c r="E23" s="3">
         <v>15000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>45000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>44000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>59000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>73000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>101000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>37000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>94000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>81000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>70000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>96000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>131000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>121000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>102000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>97000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>81000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>73000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>97000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>82000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-53000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>84000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>38000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>79000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>22000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>58000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E24" s="3">
         <v>9000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>22000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>24000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>29000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>30000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>16000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>44000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>24000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>31000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>33000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>37000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>34000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>35000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>29000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>24000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>38000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>23000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>36000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>339100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-329000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>34000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>18000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>35000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2471,216 +2520,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-825000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>20000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>43000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>82000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>21000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>50000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>57000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>39000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>63000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>94000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>87000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>67000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>68000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>58000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>49000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>59000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>75000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-76000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>8000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>48000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-301100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>311000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>30000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>45000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>23000</v>
-      </c>
-      <c r="AI26" s="3">
-        <v>16000</v>
       </c>
       <c r="AJ26" s="3">
         <v>16000</v>
       </c>
+      <c r="AK26" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-833000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11000</v>
       </c>
-      <c r="G27" s="3">
-        <v>25000</v>
-      </c>
       <c r="H27" s="3">
+        <v>28000</v>
+      </c>
+      <c r="I27" s="3">
         <v>43000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>82000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>50000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>57000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>39000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>63000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>94000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>87000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>67000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>68000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>58000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>49000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>59000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>75000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-76000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>8000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>48000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-301100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>311000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>30000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>45000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>23000</v>
-      </c>
-      <c r="AI27" s="3">
-        <v>16000</v>
       </c>
       <c r="AJ27" s="3">
         <v>16000</v>
       </c>
+      <c r="AK27" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2783,8 +2841,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2845,8 +2906,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2863,32 +2924,35 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>317100</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>3000</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-453000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2991,8 +3055,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3095,97 +3162,100 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>32000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-13000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-40000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-31000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-15000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>41000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>35000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>29000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>42000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>64000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>35000</v>
       </c>
       <c r="AA32" s="3">
         <v>35000</v>
       </c>
       <c r="AB32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1000</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AG32" s="3">
         <v>-1000</v>
@@ -3194,117 +3264,123 @@
         <v>-1000</v>
       </c>
       <c r="AI32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-825000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>23000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>30000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>43000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>82000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>21000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>50000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>57000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>39000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>63000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>94000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>87000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>67000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>68000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>58000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>49000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>59000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>75000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-76000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>8000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>48000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>16000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>311000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>33000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>45000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-449000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>23000</v>
-      </c>
-      <c r="AI33" s="3">
-        <v>16000</v>
       </c>
       <c r="AJ33" s="3">
         <v>16000</v>
       </c>
+      <c r="AK33" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3407,221 +3483,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-825000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>23000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>30000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>43000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>82000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>21000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>50000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>57000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>39000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>63000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>94000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>87000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>67000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>68000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>58000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>49000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>59000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>75000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-76000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>8000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>48000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>16000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>311000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>33000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>45000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-449000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>23000</v>
-      </c>
-      <c r="AI35" s="3">
-        <v>16000</v>
       </c>
       <c r="AJ35" s="3">
         <v>16000</v>
       </c>
+      <c r="AK35" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3658,8 +3743,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3696,101 +3782,102 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>753000</v>
+      </c>
+      <c r="E41" s="3">
         <v>577000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>692000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>531000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>413000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>603000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>636000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>368000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>381000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>292000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>326000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>252000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>251000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>244000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>779000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>686000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>579000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>508000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>517000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>260000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>362000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>338000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>122000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>132000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>142000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>212000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>265000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>184000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>93000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>75000</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3800,41 +3887,44 @@
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E42" s="3">
         <v>7000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19000</v>
-      </c>
-      <c r="H42" s="3">
-        <v>20000</v>
       </c>
       <c r="I42" s="3">
         <v>20000</v>
       </c>
       <c r="J42" s="3">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="K42" s="3">
         <v>23000</v>
       </c>
       <c r="L42" s="3">
+        <v>23000</v>
+      </c>
+      <c r="M42" s="3">
         <v>21000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3904,101 +3994,104 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1135000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1045000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1023000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1103000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1071000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>933000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>973000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>988000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1043000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>985000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1002000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1043000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1073000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1008000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>876000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>932000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>895000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>875000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>863000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>884000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>704000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>820000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>817000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>845000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>835000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>838000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>821000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>809000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>766000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>756000</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4008,101 +4101,104 @@
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1259000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1228000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1237000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1197000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1188000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>929000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>941000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>970000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1001000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1008000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>975000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>957000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>971000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>922000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>740000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>710000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>684000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>681000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>672000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>618000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>614000</v>
-      </c>
-      <c r="X44" s="3">
-        <v>671000</v>
       </c>
       <c r="Y44" s="3">
         <v>671000</v>
       </c>
       <c r="Z44" s="3">
+        <v>671000</v>
+      </c>
+      <c r="AA44" s="3">
         <v>729000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>722000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>701000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>628000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>603000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>523000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>481000</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4112,101 +4208,104 @@
       <c r="AJ44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>240000</v>
+      </c>
+      <c r="E45" s="3">
         <v>204000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>210000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>193000</v>
       </c>
       <c r="G45" s="3">
         <v>193000</v>
       </c>
       <c r="H45" s="3">
+        <v>193000</v>
+      </c>
+      <c r="I45" s="3">
         <v>192000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>173000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>266000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>174000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>189000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>199000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>198000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>186000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>165000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>146000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>179000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>198000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>156000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>173000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>161000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>163000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>164000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>175000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>134000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>147000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>111000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>95000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>72000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>74000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>65000</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4216,101 +4315,104 @@
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3392000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3061000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3172000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3037000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2884000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2677000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2743000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2615000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2622000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2495000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2502000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2450000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2481000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2339000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2541000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2507000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2356000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2220000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2225000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1923000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1843000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1993000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1785000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1840000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1846000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1862000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1809000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1668000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1456000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1377000</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4320,41 +4422,44 @@
       <c r="AJ46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>10000</v>
       </c>
       <c r="I47" s="3">
         <v>10000</v>
       </c>
       <c r="J47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K47" s="3">
         <v>18000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>17000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4424,101 +4529,104 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>695000</v>
+      </c>
+      <c r="E48" s="3">
         <v>652000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>658000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>648000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>658000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>552000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>582000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>577000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>580000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>571000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>557000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>538000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>535000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>514000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>428000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>424000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>438000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>442000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>451000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>445000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>440000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>433000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>453000</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>436000</v>
       </c>
       <c r="AA48" s="3">
         <v>436000</v>
       </c>
       <c r="AB48" s="3">
+        <v>436000</v>
+      </c>
+      <c r="AC48" s="3">
         <v>413000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>300000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>276000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>264000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>267000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4528,101 +4636,104 @@
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4263000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4241000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4248000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4316000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4297000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3145000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3166000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3143000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3204000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3207000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3199000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3138000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3158000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3125000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2661000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2671000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2682000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2675000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2691000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2657000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2638000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2612000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2769000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2757000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2777000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2772000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2767000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2776000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2766000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2810000</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4632,8 +4743,11 @@
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4736,8 +4850,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4840,101 +4957,104 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>118000</v>
+        <v>164000</v>
       </c>
       <c r="E52" s="3">
         <v>118000</v>
       </c>
       <c r="F52" s="3">
+        <v>118000</v>
+      </c>
+      <c r="G52" s="3">
         <v>132000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>137000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>136000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>144000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>106000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>110000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>109000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>129000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>136000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>142000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>267000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>223000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>232000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>236000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>239000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>243000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>244000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>245000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>249000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>121000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>100000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>101000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>97000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>96000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>22000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>21000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>28000</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4944,8 +5064,11 @@
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5048,101 +5171,104 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8515000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8074000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8199000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8135000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7984000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6520000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6645000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6459000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6536000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6399000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6387000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6262000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6316000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6245000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5853000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5834000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5712000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5576000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5610000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5269000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5166000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5287000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5128000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5133000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5160000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5144000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4972000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4742000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4507000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4482000</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5152,8 +5278,11 @@
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5190,8 +5319,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5228,101 +5358,102 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1102000</v>
+      </c>
+      <c r="E57" s="3">
         <v>971000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1073000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1021000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>980000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>858000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>905000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>863000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>948000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>894000</v>
       </c>
       <c r="M57" s="3">
         <v>894000</v>
       </c>
       <c r="N57" s="3">
+        <v>894000</v>
+      </c>
+      <c r="O57" s="3">
         <v>936000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>987000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>958000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>883000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>905000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>915000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>908000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>936000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>858000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>811000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>906000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>920000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>932000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1009000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1013000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>964000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>850000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>774000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>712000</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5332,40 +5463,43 @@
       <c r="AJ57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E58" s="3">
         <v>59000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>57000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>56000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>64000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>50000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>51000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>48000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>50000</v>
       </c>
       <c r="L58" s="3">
         <v>50000</v>
       </c>
       <c r="M58" s="3">
-        <v>12000</v>
+        <v>50000</v>
       </c>
       <c r="N58" s="3">
         <v>12000</v>
@@ -5377,7 +5511,7 @@
         <v>12000</v>
       </c>
       <c r="Q58" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="R58" s="3">
         <v>10000</v>
@@ -5389,25 +5523,25 @@
         <v>10000</v>
       </c>
       <c r="U58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="V58" s="3">
         <v>7000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>181000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>287000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>382000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>22000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>88000</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>22000</v>
       </c>
       <c r="AB58" s="3">
         <v>22000</v>
@@ -5415,8 +5549,8 @@
       <c r="AC58" s="3">
         <v>22000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
+      <c r="AD58" s="3">
+        <v>22000</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>8</v>
@@ -5436,101 +5570,104 @@
       <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1838000</v>
+      </c>
+      <c r="E59" s="3">
         <v>238000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>262000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>236000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>196000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>216000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>232000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>253000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>198000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>210000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>640000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>594000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>580000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>576000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>601000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>617000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>586000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>528000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>595000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>606000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>564000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>467000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>552000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>531000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>528000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>524000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>503000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>550000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>459000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>418000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5540,101 +5677,104 @@
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3382000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1578000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1790000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1672000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1594000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1385000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1525000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1467000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1524000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1469000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1546000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1542000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1579000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1546000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1494000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1532000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1511000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1446000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1538000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1645000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1662000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1755000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1494000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1551000</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>1559000</v>
       </c>
       <c r="AB60" s="3">
         <v>1559000</v>
       </c>
       <c r="AC60" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="AD60" s="3">
         <v>1489000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1400000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1233000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1130000</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5644,92 +5784,95 @@
       <c r="AJ60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2215000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2190000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2195000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2177000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2181000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1553000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1562000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1571000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1566000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1568000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1404000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1407000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1410000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1412000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1220000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1222000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1184000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1186000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1155000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1006000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1011000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1149000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1158000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1165000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1169000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1174000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1179000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5748,101 +5891,104 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>304000</v>
+      </c>
+      <c r="E62" s="3">
         <v>959000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>805000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>932000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>915000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>813000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>692000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>776000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>769000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>758000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>908000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>913000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>933000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>926000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>887000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>922000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>914000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>912000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>924000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1013000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>998000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>862000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>874000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>844000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>839000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>819000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>771000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>657000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>794000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>763000</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5852,8 +5998,11 @@
       <c r="AJ62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5956,8 +6105,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6060,8 +6212,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6164,101 +6319,104 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5901000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4727000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4890000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4781000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4690000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3751000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3896000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3814000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3859000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3795000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3858000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3862000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3922000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3884000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3601000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3676000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3609000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3544000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3617000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3664000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3671000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3766000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3526000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3560000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3567000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3552000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3439000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2057000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2027000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1893000</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6268,8 +6426,11 @@
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6306,8 +6467,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6410,8 +6572,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6514,8 +6679,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6532,7 +6700,7 @@
         <v>482000</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>482000</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -6618,8 +6786,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6722,92 +6893,95 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E72" s="3">
         <v>904000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>907000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>893000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>881000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>853000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>810000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>728000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>707000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>657000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>600000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>561000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>498000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>404000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>317000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>250000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>182000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>124000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>75000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>16000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-59000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>17000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>38000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>47000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>39000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>50000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2000</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6826,8 +7000,11 @@
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6930,8 +7107,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7034,8 +7214,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7138,101 +7321,104 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2132000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2865000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2827000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2872000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2812000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2769000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2749000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2645000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2677000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2604000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2529000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2400000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2394000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2361000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2252000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2158000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2103000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2032000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1993000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1605000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1495000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1521000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1602000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1573000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1593000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1592000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1533000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2685000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2480000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2589000</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7242,8 +7428,11 @@
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7346,221 +7535,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-825000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>23000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>30000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>43000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>82000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>21000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>50000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>57000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>39000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>63000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>94000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>87000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>67000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>68000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>58000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>49000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>59000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>75000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-76000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>8000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>48000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>16000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>311000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>33000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>45000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-449000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>23000</v>
-      </c>
-      <c r="AI81" s="3">
-        <v>16000</v>
       </c>
       <c r="AJ81" s="3">
         <v>16000</v>
       </c>
+      <c r="AK81" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7597,8 +7795,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7606,91 +7805,91 @@
         <v>15000</v>
       </c>
       <c r="E83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F83" s="3">
         <v>17000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>15000</v>
       </c>
       <c r="J83" s="3">
         <v>15000</v>
       </c>
       <c r="K83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L83" s="3">
         <v>9000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>21000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>22000</v>
       </c>
       <c r="S83" s="3">
         <v>22000</v>
       </c>
       <c r="T83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="U83" s="3">
         <v>23000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>22000</v>
       </c>
       <c r="V83" s="3">
         <v>22000</v>
       </c>
       <c r="W83" s="3">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="X83" s="3">
         <v>21000</v>
       </c>
       <c r="Y83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>25000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>19000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>16000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>17000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>16000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>13000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>20000</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>17000</v>
       </c>
       <c r="AH83" s="3">
         <v>17000</v>
@@ -7699,10 +7898,13 @@
         <v>17000</v>
       </c>
       <c r="AJ83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AK83" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7805,8 +8007,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7909,8 +8114,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8013,8 +8221,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8117,8 +8328,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8221,112 +8435,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-65000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>203000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>147000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>92000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>263000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>60000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>121000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>139000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>37000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>112000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>104000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>94000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>152000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>145000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-74000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>93000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-33000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-27000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>87000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>117000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>132000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>126000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-143000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>111000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8363,112 +8583,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-22000</v>
       </c>
       <c r="F91" s="3">
         <v>-22000</v>
       </c>
       <c r="G91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-15000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-21000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-31000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-29000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-51000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-23000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8571,8 +8795,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8675,112 +8902,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1342000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>46000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-35000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-57000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-37000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-665000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-18000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-24000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-51000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-34000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8817,8 +9050,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8849,8 +9083,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8921,8 +9155,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9025,8 +9262,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9129,8 +9369,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9233,316 +9476,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1060000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-29000</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-9000</v>
       </c>
       <c r="L100" s="3">
         <v>-9000</v>
       </c>
       <c r="M100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N100" s="3">
         <v>-12000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>189000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>21000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>118000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-106000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-108000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>349000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-75000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>53000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-23000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>19000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>15000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-102000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>157000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-88000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-28000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-25000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-13000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-13000</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>2000</v>
       </c>
       <c r="W101" s="3">
         <v>2000</v>
       </c>
       <c r="X101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>2000</v>
       </c>
       <c r="AI101" s="3">
         <v>2000</v>
       </c>
       <c r="AJ101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AK101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>176000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-115000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>161000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>118000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-190000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>267000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>87000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-33000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>74000</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>11000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-535000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>93000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>107000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>71000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>257000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-102000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>24000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>216000</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>-10000</v>
       </c>
       <c r="Z102" s="3">
         <v>-10000</v>
       </c>
       <c r="AA102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-70000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>81000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>91000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>18000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>19000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>10000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>REZI</t>
   </si>
@@ -656,490 +656,502 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1895000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1864000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1943000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1770000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1858000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1828000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1589000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1486000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1537000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1554000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1602000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1549000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1560000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1618000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1686000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1506000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1454000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1496000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1477000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1419000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1501000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1362000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1029000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1179000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1304000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1226000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1242000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1216000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1266000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1200000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1196000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1165000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1209000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1152000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1096000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1062000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1335000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1308000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1374000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1259000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1328000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1304000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1142000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1086000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1114000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1137000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1166000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1131000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1129000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1188000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1219000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1072000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1058000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1080000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1096000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1051000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1076000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>990000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>789000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>892000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>930000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>932000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>933000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>903000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>936000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>853000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>850000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>822000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>848000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>816000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>788000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>751000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>560000</v>
+      </c>
+      <c r="E10" s="3">
         <v>556000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>569000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>511000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>530000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>524000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>447000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>400000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>423000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>417000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>436000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>418000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>431000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>430000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>467000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>434000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>396000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>416000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>381000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>368000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>425000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>372000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>240000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>287000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>374000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>294000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>309000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>313000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>330000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>347000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>346000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>343000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>361000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>336000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>308000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>311000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1178,68 +1190,69 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E12" s="3">
         <v>44000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>41000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>35000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>42000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>21000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>25000</v>
       </c>
       <c r="K12" s="3">
         <v>25000</v>
       </c>
       <c r="L12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="M12" s="3">
         <v>28000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>25000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>30000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>29000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>28000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>23000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>22000</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1288,8 +1301,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1398,100 +1414,103 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>884000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>94000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>115000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>74000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>58000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>50000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>54000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>81000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>46000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>76000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>43000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>45000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>41000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>35000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>57000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>36000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>59000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>13000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>7000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>11000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>9000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-17000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>10000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>40000</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1508,8 +1527,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,47 +1539,47 @@
         <v>31000</v>
       </c>
       <c r="E15" s="3">
-        <v>30000</v>
+        <v>31000</v>
       </c>
       <c r="F15" s="3">
         <v>30000</v>
       </c>
       <c r="G15" s="3">
-        <v>29000</v>
+        <v>30000</v>
       </c>
       <c r="H15" s="3">
         <v>29000</v>
       </c>
       <c r="I15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="J15" s="3">
         <v>13000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>10000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>9000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>10000</v>
       </c>
       <c r="P15" s="3">
         <v>10000</v>
       </c>
       <c r="Q15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="R15" s="3">
         <v>9000</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1573,8 +1595,8 @@
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1618,8 +1640,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1655,228 +1680,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1723000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1707000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1764000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1630000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1679000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1673000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1456000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1351000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1399000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1407000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1447000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1409000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1503000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1506000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1545000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1375000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1348000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1386000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1392000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1348000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1349000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1231000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1035000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1145000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1232000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1167000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1200000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1131000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1208000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1218000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1190000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1188000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1095000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1057000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1015000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E18" s="3">
         <v>157000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>179000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>140000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>179000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>155000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>133000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>135000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>138000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>147000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>155000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>140000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>57000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>112000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>141000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>131000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>106000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>110000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>85000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>71000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>152000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>131000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>34000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>72000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>59000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>42000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>85000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>58000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>78000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>57000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>39000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1915,103 +1947,104 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>7000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>10000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-32000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>40000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>31000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>8000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>15000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-41000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-42000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-64000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-35000</v>
       </c>
       <c r="AC20" s="3">
         <v>-35000</v>
       </c>
       <c r="AD20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="AE20" s="3">
         <v>16000</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>1000</v>
       </c>
       <c r="AI20" s="3">
         <v>1000</v>
@@ -2020,213 +2053,219 @@
         <v>1000</v>
       </c>
       <c r="AK20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>209000</v>
+      </c>
+      <c r="E21" s="3">
         <v>181000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>200000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>164000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>215000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>174000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>145000</v>
       </c>
       <c r="J21" s="3">
         <v>145000</v>
       </c>
       <c r="K21" s="3">
+        <v>145000</v>
+      </c>
+      <c r="L21" s="3">
         <v>180000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>143000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>167000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>109000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>113000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>135000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>170000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>152000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>134000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>131000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>115000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>109000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>133000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>118000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>13000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>33000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>43000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>27000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>117000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>75000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>21000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>96000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>75000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>56000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E22" s="3">
         <v>37000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>24000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>26000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>17000</v>
       </c>
       <c r="N22" s="3">
         <v>17000</v>
       </c>
       <c r="O22" s="3">
+        <v>17000</v>
+      </c>
+      <c r="P22" s="3">
         <v>18000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>14000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>11000</v>
       </c>
       <c r="S22" s="3">
         <v>11000</v>
       </c>
       <c r="T22" s="3">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="U22" s="3">
         <v>12000</v>
       </c>
       <c r="V22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="W22" s="3">
         <v>13000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>14000</v>
       </c>
       <c r="X22" s="3">
         <v>14000</v>
       </c>
       <c r="Y22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>18000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>17000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>18000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>18000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>17000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>20000</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2245,228 +2284,237 @@
       <c r="AL22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E23" s="3">
         <v>110000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-738000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>45000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>44000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>59000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>73000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>101000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>37000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>94000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>81000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>70000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>96000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>131000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>121000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>102000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>97000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>81000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>73000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>97000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>82000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>84000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>38000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>79000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>58000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>39000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-46000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>87000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>22000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>24000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>29000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>30000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>44000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>24000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>31000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>33000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>37000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>34000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>35000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>29000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>23000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>24000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>38000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>23000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>36000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>339100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-329000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>34000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>35000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>23000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2575,228 +2623,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E26" s="3">
         <v>156000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-825000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>20000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>43000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>82000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>50000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>57000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>39000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>63000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>94000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>87000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>67000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>68000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>58000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>49000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>59000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>75000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>48000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-301100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>311000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>30000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>45000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>23000</v>
-      </c>
-      <c r="AK26" s="3">
-        <v>16000</v>
       </c>
       <c r="AL26" s="3">
         <v>16000</v>
       </c>
+      <c r="AM26" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E27" s="3">
         <v>131000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-817000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>25000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>43000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>82000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>50000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>57000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>39000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>63000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>94000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>87000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>67000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>68000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>58000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>49000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>59000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>75000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>8000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>48000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-301100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>311000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>30000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>45000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>23000</v>
-      </c>
-      <c r="AK27" s="3">
-        <v>16000</v>
       </c>
       <c r="AL27" s="3">
         <v>16000</v>
       </c>
+      <c r="AM27" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2905,8 +2962,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2973,8 +3033,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2991,32 +3051,35 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>317100</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>3000</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-453000</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3125,8 +3188,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3235,103 +3301,106 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-10000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>32000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-40000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-31000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-8000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-15000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>41000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>35000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>29000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>42000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>64000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>35000</v>
       </c>
       <c r="AC32" s="3">
         <v>35000</v>
       </c>
       <c r="AD32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AI32" s="3">
         <v>-1000</v>
@@ -3340,123 +3409,129 @@
         <v>-1000</v>
       </c>
       <c r="AK32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E33" s="3">
         <v>156000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-825000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>20000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>30000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>43000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>82000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>50000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>57000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>39000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>63000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>94000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>87000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>67000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>68000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>58000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>49000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>59000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>75000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>8000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>48000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>16000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>311000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>33000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>45000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-449000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>23000</v>
-      </c>
-      <c r="AK33" s="3">
-        <v>16000</v>
       </c>
       <c r="AL33" s="3">
         <v>16000</v>
       </c>
+      <c r="AM33" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3565,233 +3640,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E35" s="3">
         <v>156000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-825000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>20000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>30000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>43000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>82000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>50000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>57000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>39000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>63000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>94000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>87000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>67000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>68000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>58000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>49000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>59000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>75000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>8000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>48000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>16000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>311000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>33000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>45000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-449000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>23000</v>
-      </c>
-      <c r="AK35" s="3">
-        <v>16000</v>
       </c>
       <c r="AL35" s="3">
         <v>16000</v>
       </c>
+      <c r="AM35" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3830,8 +3914,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3870,107 +3955,108 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>661000</v>
+      </c>
+      <c r="E41" s="3">
         <v>345000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>753000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>577000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>692000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>531000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>413000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>603000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>636000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>368000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>381000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>292000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>326000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>252000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>251000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>244000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>779000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>686000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>579000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>508000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>517000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>260000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>362000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>338000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>122000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>132000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>142000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>212000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>265000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>184000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>93000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>75000</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3980,47 +4066,50 @@
       <c r="AL41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19000</v>
-      </c>
-      <c r="J42" s="3">
-        <v>20000</v>
       </c>
       <c r="K42" s="3">
         <v>20000</v>
       </c>
       <c r="L42" s="3">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="M42" s="3">
         <v>23000</v>
       </c>
       <c r="N42" s="3">
+        <v>23000</v>
+      </c>
+      <c r="O42" s="3">
         <v>21000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4090,107 +4179,110 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1073000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1147000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1135000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1045000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1023000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1103000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1071000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>933000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>973000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>988000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1043000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>985000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1002000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1043000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1073000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1008000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>876000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>932000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>895000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>875000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>863000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>884000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>704000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>820000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>817000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>845000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>835000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>838000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>821000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>809000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>766000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>756000</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4200,107 +4292,110 @@
       <c r="AL43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1354000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1328000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1259000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1228000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1237000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1197000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1188000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>929000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>941000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>970000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1001000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1008000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>975000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>957000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>971000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>922000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>740000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>710000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>684000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>681000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>672000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>618000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>614000</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>671000</v>
       </c>
       <c r="AA44" s="3">
         <v>671000</v>
       </c>
       <c r="AB44" s="3">
+        <v>671000</v>
+      </c>
+      <c r="AC44" s="3">
         <v>729000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>722000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>701000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>628000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>603000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>523000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>481000</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4310,107 +4405,110 @@
       <c r="AL44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E45" s="3">
         <v>249000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>240000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>204000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>210000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>193000</v>
       </c>
       <c r="I45" s="3">
         <v>193000</v>
       </c>
       <c r="J45" s="3">
+        <v>193000</v>
+      </c>
+      <c r="K45" s="3">
         <v>192000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>173000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>266000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>174000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>189000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>199000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>198000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>186000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>165000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>146000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>179000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>198000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>156000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>173000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>161000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>163000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>164000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>175000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>134000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>147000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>111000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>95000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>72000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>74000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>65000</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4420,107 +4518,110 @@
       <c r="AL45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3358000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3072000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3392000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3061000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3172000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3037000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2884000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2677000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2743000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2615000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2622000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2495000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2502000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2450000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2481000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2339000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2541000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2507000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2356000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2220000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2225000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1923000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1843000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1993000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1785000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1840000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1846000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1862000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1809000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1668000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1456000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1377000</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4530,8 +4631,11 @@
       <c r="AL46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4542,35 +4646,35 @@
         <v>1000</v>
       </c>
       <c r="F47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G47" s="3">
         <v>2000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>10000</v>
       </c>
       <c r="K47" s="3">
         <v>10000</v>
       </c>
       <c r="L47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="M47" s="3">
         <v>18000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>17000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4640,107 +4744,110 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>774000</v>
+      </c>
+      <c r="E48" s="3">
         <v>764000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>695000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>652000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>658000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>648000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>658000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>552000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>582000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>577000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>580000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>571000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>557000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>538000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>535000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>514000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>428000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>424000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>438000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>442000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>451000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>445000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>440000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>433000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>453000</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>436000</v>
       </c>
       <c r="AC48" s="3">
         <v>436000</v>
       </c>
       <c r="AD48" s="3">
+        <v>436000</v>
+      </c>
+      <c r="AE48" s="3">
         <v>413000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>300000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>276000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>264000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>267000</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4750,107 +4857,110 @@
       <c r="AL48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4191000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4235000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4263000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4241000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4248000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4316000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4297000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3145000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3166000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3143000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3204000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3207000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3199000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3138000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3158000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3125000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2661000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2671000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2682000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2675000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2691000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2657000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2638000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2612000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2769000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2757000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2777000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2772000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2767000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2776000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2766000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2810000</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4860,8 +4970,11 @@
       <c r="AL49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4970,8 +5083,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5080,107 +5196,110 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E52" s="3">
         <v>116000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>164000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>118000</v>
       </c>
       <c r="G52" s="3">
         <v>118000</v>
       </c>
       <c r="H52" s="3">
+        <v>118000</v>
+      </c>
+      <c r="I52" s="3">
         <v>132000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>137000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>136000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>144000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>106000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>110000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>109000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>129000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>136000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>142000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>267000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>223000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>232000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>236000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>239000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>243000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>244000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>245000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>249000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>121000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>100000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>101000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>97000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>96000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>22000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>21000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>28000</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5190,8 +5309,11 @@
       <c r="AL52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5300,107 +5422,110 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8433000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8188000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8515000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8074000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8199000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8135000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7984000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6520000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6645000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6459000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6536000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6399000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6387000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6262000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6316000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6245000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5853000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5834000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5712000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5576000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5610000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5269000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5166000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5287000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5128000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5133000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5160000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5144000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4972000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4742000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4507000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4482000</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5410,8 +5535,11 @@
       <c r="AL54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5450,8 +5578,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5490,107 +5619,108 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1131000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1037000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1102000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>971000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1073000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1021000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>980000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>858000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>905000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>863000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>948000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>894000</v>
       </c>
       <c r="O57" s="3">
         <v>894000</v>
       </c>
       <c r="P57" s="3">
+        <v>894000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>936000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>987000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>958000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>883000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>905000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>915000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>908000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>936000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>858000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>811000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>906000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>920000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>932000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1009000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1013000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>964000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>850000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>774000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>712000</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5600,46 +5730,49 @@
       <c r="AL57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E58" s="3">
         <v>82000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>66000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>59000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>57000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>56000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>64000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>50000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>51000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>48000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>50000</v>
       </c>
       <c r="N58" s="3">
         <v>50000</v>
       </c>
       <c r="O58" s="3">
-        <v>12000</v>
+        <v>50000</v>
       </c>
       <c r="P58" s="3">
         <v>12000</v>
@@ -5651,7 +5784,7 @@
         <v>12000</v>
       </c>
       <c r="S58" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="T58" s="3">
         <v>10000</v>
@@ -5663,25 +5796,25 @@
         <v>10000</v>
       </c>
       <c r="W58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="X58" s="3">
         <v>7000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>181000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>287000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>382000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>22000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>88000</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>22000</v>
       </c>
       <c r="AD58" s="3">
         <v>22000</v>
@@ -5689,8 +5822,8 @@
       <c r="AE58" s="3">
         <v>22000</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
+      <c r="AF58" s="3">
+        <v>22000</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
@@ -5710,107 +5843,110 @@
       <c r="AL58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
         <v>1838000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>238000</v>
       </c>
-      <c r="G59" s="3">
-        <v>262000</v>
-      </c>
       <c r="H59" s="3">
+        <v>171000</v>
+      </c>
+      <c r="I59" s="3">
         <v>236000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>196000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>216000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>232000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>253000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>198000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>210000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>640000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>594000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>580000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>576000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>601000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>617000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>586000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>528000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>595000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>606000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>564000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>467000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>552000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>531000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>528000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>524000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>503000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>550000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>459000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>418000</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5820,107 +5956,110 @@
       <c r="AL59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1755000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1632000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3382000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1578000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1790000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1672000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1594000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1385000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1525000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1467000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1524000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1469000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1546000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1542000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1579000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1546000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1494000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1532000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1511000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1446000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1538000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1645000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1662000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1755000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1494000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1551000</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>1559000</v>
       </c>
       <c r="AD60" s="3">
         <v>1559000</v>
       </c>
       <c r="AE60" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="AF60" s="3">
         <v>1489000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1400000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1233000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1130000</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5930,98 +6069,101 @@
       <c r="AL60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3456000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3464000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2215000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2190000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2195000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2177000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2181000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1553000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1562000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1571000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1566000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1568000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1404000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1407000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1410000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1412000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1220000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1222000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1184000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1186000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1155000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1006000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1011000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1149000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1158000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1165000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1169000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1174000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1179000</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -6040,107 +6182,110 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E62" s="3">
         <v>321000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>304000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>959000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>805000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>932000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>915000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>813000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>692000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>776000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>769000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>758000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>908000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>913000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>933000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>926000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>887000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>922000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>914000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>912000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>924000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1013000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>998000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>862000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>874000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>844000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>839000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>819000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>771000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>657000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>794000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>763000</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6150,8 +6295,11 @@
       <c r="AL62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6260,8 +6408,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6370,8 +6521,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6480,107 +6634,110 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5516000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5417000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5901000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4727000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4890000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4781000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4690000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3751000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3896000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3814000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3859000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3795000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3858000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3862000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3922000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3884000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3601000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3676000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3609000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3544000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3617000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3664000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3671000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3766000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3526000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3560000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3567000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3552000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3439000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2057000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2027000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1893000</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6590,8 +6747,11 @@
       <c r="AL66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6630,8 +6790,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6740,8 +6901,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6850,8 +7014,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6874,7 +7041,7 @@
         <v>482000</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>482000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -6960,8 +7127,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7070,98 +7240,101 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E72" s="3">
         <v>218000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>71000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>904000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>907000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>893000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>881000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>853000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>810000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>728000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>707000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>657000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>600000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>561000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>498000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>404000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>317000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>250000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>182000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>124000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>75000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>16000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-59000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>38000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>47000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>39000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>50000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2000</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7180,8 +7353,11 @@
       <c r="AL72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7290,8 +7466,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7400,8 +7579,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7510,107 +7692,110 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2435000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2289000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2132000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2865000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2827000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2872000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2812000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2769000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2749000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2645000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2677000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2604000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2529000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2400000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2394000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2361000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2252000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2158000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2103000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2032000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1993000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1605000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1495000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1521000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1602000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1573000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1593000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1592000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1533000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2685000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2480000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2589000</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7620,8 +7805,11 @@
       <c r="AL76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7730,233 +7918,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E81" s="3">
         <v>156000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-825000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>20000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>30000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>43000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>82000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>50000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>57000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>39000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>63000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>94000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>87000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>67000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>68000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>58000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>49000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>59000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>75000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>8000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>48000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>16000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>311000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>33000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>45000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-449000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>23000</v>
-      </c>
-      <c r="AK81" s="3">
-        <v>16000</v>
       </c>
       <c r="AL81" s="3">
         <v>16000</v>
       </c>
+      <c r="AM81" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7995,8 +8192,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8004,97 +8202,97 @@
         <v>17000</v>
       </c>
       <c r="E83" s="3">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="F83" s="3">
         <v>15000</v>
       </c>
       <c r="G83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="H83" s="3">
         <v>17000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>15000</v>
       </c>
       <c r="L83" s="3">
         <v>15000</v>
       </c>
       <c r="M83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="N83" s="3">
         <v>9000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>25000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>20000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>21000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>22000</v>
       </c>
       <c r="U83" s="3">
         <v>22000</v>
       </c>
       <c r="V83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="W83" s="3">
         <v>23000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>22000</v>
       </c>
       <c r="X83" s="3">
         <v>22000</v>
       </c>
       <c r="Y83" s="3">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="Z83" s="3">
         <v>21000</v>
       </c>
       <c r="AA83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AB83" s="3">
         <v>25000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>20000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>16000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>17000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>16000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>13000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>20000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>17000</v>
       </c>
       <c r="AJ83" s="3">
         <v>17000</v>
@@ -8103,10 +8301,13 @@
         <v>17000</v>
       </c>
       <c r="AL83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AM83" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8215,8 +8416,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8325,8 +8529,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8435,8 +8642,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8545,8 +8755,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8655,118 +8868,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1571000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>200000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-65000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>203000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>147000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>92000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>263000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>60000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>121000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>139000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>37000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>35000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-59000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>112000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>104000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>94000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>152000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>21000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>145000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-74000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>93000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-33000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-27000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>87000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>117000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>132000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>126000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-143000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>111000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>30000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8805,118 +9024,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-22000</v>
       </c>
       <c r="H91" s="3">
         <v>-22000</v>
       </c>
       <c r="I91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-15000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-29000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-51000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-20000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-23000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9025,8 +9248,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9135,118 +9361,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-20000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1342000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>46000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-35000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-29000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-26000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-57000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-665000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-14000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-24000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-18000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-34000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-21000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-39000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9285,8 +9517,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9323,8 +9556,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9395,8 +9628,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9505,8 +9741,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9615,8 +9854,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9725,334 +9967,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1192000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-22000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1060000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-29000</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-9000</v>
       </c>
       <c r="N100" s="3">
         <v>-9000</v>
       </c>
       <c r="O100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="P100" s="3">
         <v>-12000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>189000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>21000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>13000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>118000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-106000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-108000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>349000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-75000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>53000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-23000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>19000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>15000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-102000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>157000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-88000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-28000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-25000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-13000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-13000</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>2000</v>
       </c>
       <c r="Y101" s="3">
         <v>2000</v>
       </c>
       <c r="Z101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AJ101" s="3">
-        <v>2000</v>
       </c>
       <c r="AK101" s="3">
         <v>2000</v>
       </c>
       <c r="AL101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AM101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>316000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-408000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>176000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-115000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>161000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>118000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-190000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-33000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>267000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>87000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-33000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>74000</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>11000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-535000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>93000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>107000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>71000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>257000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-102000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>24000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>216000</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>-10000</v>
       </c>
       <c r="AB102" s="3">
         <v>-10000</v>
       </c>
       <c r="AC102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-70000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>81000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>91000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>18000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>19000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>10000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>3000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-3000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REZI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>REZI</t>
   </si>
@@ -656,502 +656,515 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44380</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44289</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1912000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1895000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1864000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1943000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1770000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1858000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1828000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1589000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1486000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1537000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1554000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1602000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1549000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1560000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1618000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1686000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1506000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1454000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1496000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1477000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1419000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1501000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1362000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1029000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1179000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1304000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1226000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1242000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1216000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1266000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1200000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1196000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1165000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1209000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1152000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1096000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1062000</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1361000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1335000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1308000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1374000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1259000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1328000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1304000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1142000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1086000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1114000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1137000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1166000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1131000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1129000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1188000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1219000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1072000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1058000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1080000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1096000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1051000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1076000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>990000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>789000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>892000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>930000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>932000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>933000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>903000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>936000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>853000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>850000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>822000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>848000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>816000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>788000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>751000</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E10" s="3">
         <v>560000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>556000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>569000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>511000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>530000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>524000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>447000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>400000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>423000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>417000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>436000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>418000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>431000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>430000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>467000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>434000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>396000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>416000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>381000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>368000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>425000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>372000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>240000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>287000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>374000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>294000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>309000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>313000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>330000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>347000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>346000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>343000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>361000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>336000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>308000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>311000</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1191,71 +1204,72 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E12" s="3">
         <v>47000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>44000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>41000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>35000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>42000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>25000</v>
       </c>
       <c r="L12" s="3">
         <v>25000</v>
       </c>
       <c r="M12" s="3">
+        <v>25000</v>
+      </c>
+      <c r="N12" s="3">
         <v>28000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>30000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>29000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>28000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>23000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>20000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>22000</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1304,8 +1318,11 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1417,103 +1434,106 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-27000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>884000</v>
       </c>
-      <c r="G14" s="3">
-        <v>94000</v>
-      </c>
       <c r="H14" s="3">
+        <v>93000</v>
+      </c>
+      <c r="I14" s="3">
         <v>115000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>74000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>58000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>50000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>54000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>81000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>46000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>76000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>43000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>45000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>41000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>35000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>57000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>36000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>59000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>13000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>7000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>11000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>9000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-17000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>10000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>40000</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1530,8 +1550,11 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1542,47 +1565,47 @@
         <v>31000</v>
       </c>
       <c r="F15" s="3">
-        <v>30000</v>
+        <v>31000</v>
       </c>
       <c r="G15" s="3">
         <v>30000</v>
       </c>
       <c r="H15" s="3">
-        <v>29000</v>
+        <v>30000</v>
       </c>
       <c r="I15" s="3">
         <v>29000</v>
       </c>
       <c r="J15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="K15" s="3">
         <v>13000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>10000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>10000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>9000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>10000</v>
       </c>
       <c r="Q15" s="3">
         <v>10000</v>
       </c>
       <c r="R15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="S15" s="3">
         <v>9000</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1598,8 +1621,8 @@
       <c r="X15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1643,8 +1666,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1681,234 +1707,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1761000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1723000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1707000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1764000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1630000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1679000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1673000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1456000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1351000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1399000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1407000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1447000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1409000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1503000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1506000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1545000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1375000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1348000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1386000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1392000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1348000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1349000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1231000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1035000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1145000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1232000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1167000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1200000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1131000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1208000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1218000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1190000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1188000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1095000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1057000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1015000</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E18" s="3">
         <v>172000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>157000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>179000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>140000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>179000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>155000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>133000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>135000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>138000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>147000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>155000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>140000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>57000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>112000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>141000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>131000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>106000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>110000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>85000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>71000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>152000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>131000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>34000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>72000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>59000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>42000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>85000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>58000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>78000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>21000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>57000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>39000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1948,106 +1981,107 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9000</v>
       </c>
-      <c r="G20" s="3">
-        <v>6000</v>
-      </c>
       <c r="H20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-7000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-32000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>13000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>40000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>31000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>8000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>15000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-42000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-64000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-35000</v>
       </c>
       <c r="AD20" s="3">
         <v>-35000</v>
       </c>
       <c r="AE20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="AF20" s="3">
         <v>16000</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>1000</v>
       </c>
       <c r="AJ20" s="3">
         <v>1000</v>
@@ -2056,219 +2090,225 @@
         <v>1000</v>
       </c>
       <c r="AL20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" s="3">
         <v>0</v>
       </c>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E21" s="3">
         <v>209000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>181000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>200000</v>
       </c>
-      <c r="G21" s="3">
-        <v>164000</v>
-      </c>
       <c r="H21" s="3">
+        <v>163000</v>
+      </c>
+      <c r="I21" s="3">
         <v>215000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>174000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>145000</v>
       </c>
       <c r="K21" s="3">
         <v>145000</v>
       </c>
       <c r="L21" s="3">
+        <v>145000</v>
+      </c>
+      <c r="M21" s="3">
         <v>180000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>143000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>167000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>109000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>113000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>135000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>170000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>152000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>134000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>131000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>115000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>109000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>133000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>118000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>13000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>33000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>43000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>27000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>117000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>75000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>21000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>39000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>75000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>56000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E22" s="3">
         <v>49000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>37000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>24000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>26000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>27000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>15000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>17000</v>
       </c>
       <c r="O22" s="3">
         <v>17000</v>
       </c>
       <c r="P22" s="3">
+        <v>17000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>18000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>15000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>14000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>11000</v>
       </c>
       <c r="T22" s="3">
         <v>11000</v>
       </c>
       <c r="U22" s="3">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="V22" s="3">
         <v>12000</v>
       </c>
       <c r="W22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="X22" s="3">
         <v>13000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>14000</v>
       </c>
       <c r="Y22" s="3">
         <v>14000</v>
       </c>
       <c r="Z22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>18000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>17000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>18000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>16000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>18000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>17000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20000</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2287,234 +2327,243 @@
       <c r="AM22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E23" s="3">
         <v>156000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>110000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-738000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>45000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>44000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>59000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>73000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>101000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>37000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>94000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>81000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>70000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>96000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>131000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>121000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>102000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>97000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>81000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>73000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>97000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>82000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-53000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>84000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>38000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>79000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>22000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>58000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>39000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E24" s="3">
         <v>20000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-46000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>87000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>24000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>29000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>30000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>44000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>24000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>31000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>33000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>37000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>34000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>35000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>29000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>23000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>24000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>38000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>23000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>36000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>339100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-329000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>18000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>35000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>23000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2626,234 +2675,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E26" s="3">
         <v>136000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>156000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-825000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>23000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>43000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>82000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>50000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>57000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>39000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>63000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>94000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>87000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>67000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>68000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>58000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>49000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>59000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>75000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>48000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-301100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>311000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>30000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>45000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>23000</v>
-      </c>
-      <c r="AL26" s="3">
-        <v>16000</v>
       </c>
       <c r="AM26" s="3">
         <v>16000</v>
       </c>
+      <c r="AN26" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E27" s="3">
         <v>127000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>131000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-817000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>25000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>43000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>82000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>50000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>57000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>39000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>63000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>94000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>87000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>67000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>68000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>58000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>49000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>59000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>75000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>8000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>48000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-301100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>311000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>30000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>45000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>23000</v>
-      </c>
-      <c r="AL27" s="3">
-        <v>16000</v>
       </c>
       <c r="AM27" s="3">
         <v>16000</v>
       </c>
+      <c r="AN27" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2965,8 +3023,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3036,8 +3097,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3054,32 +3115,35 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>317100</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>3000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-453000</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3191,8 +3255,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3304,106 +3371,109 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>6000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-6000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="I32" s="3">
         <v>7000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>32000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-13000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-40000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-8000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-15000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>41000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>35000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>29000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>42000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>64000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>35000</v>
       </c>
       <c r="AD32" s="3">
         <v>35000</v>
       </c>
       <c r="AE32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>1000</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AJ32" s="3">
         <v>-1000</v>
@@ -3412,126 +3482,132 @@
         <v>-1000</v>
       </c>
       <c r="AL32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AM32" s="3">
         <v>0</v>
       </c>
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E33" s="3">
         <v>136000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>156000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-825000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>23000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>43000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>82000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>50000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>57000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>39000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>63000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>94000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>87000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>67000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>68000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>58000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>49000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>59000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>75000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>48000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>16000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>311000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>33000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>45000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-449000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>23000</v>
-      </c>
-      <c r="AL33" s="3">
-        <v>16000</v>
       </c>
       <c r="AM33" s="3">
         <v>16000</v>
       </c>
+      <c r="AN33" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3643,239 +3719,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E35" s="3">
         <v>136000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>156000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-825000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>23000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>43000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>82000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>50000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>57000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>39000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>63000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>94000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>87000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>67000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>68000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>58000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>49000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>59000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>75000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>48000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>16000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>311000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>33000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>45000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-449000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>23000</v>
-      </c>
-      <c r="AL35" s="3">
-        <v>16000</v>
       </c>
       <c r="AM35" s="3">
         <v>16000</v>
       </c>
+      <c r="AN35" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44380</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44289</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3915,8 +4000,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3956,110 +4042,111 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E41" s="3">
         <v>661000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>345000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>753000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>577000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>692000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>531000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>413000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>603000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>636000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>368000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>381000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>292000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>326000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>252000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>251000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>244000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>779000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>686000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>579000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>508000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>517000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>260000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>362000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>338000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>122000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>132000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>142000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>212000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>265000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>184000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>93000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>8</v>
       </c>
@@ -4069,8 +4156,11 @@
       <c r="AM41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4078,41 +4168,41 @@
         <v>2000</v>
       </c>
       <c r="E42" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F42" s="3">
         <v>3000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>19000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>20000</v>
       </c>
       <c r="L42" s="3">
         <v>20000</v>
       </c>
       <c r="M42" s="3">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="N42" s="3">
         <v>23000</v>
       </c>
       <c r="O42" s="3">
+        <v>23000</v>
+      </c>
+      <c r="P42" s="3">
         <v>21000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4182,110 +4272,113 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1114000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1073000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1147000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1135000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1045000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1023000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1103000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1071000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>933000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>973000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>988000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1043000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>985000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1002000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1043000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1073000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1008000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>876000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>932000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>895000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>875000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>863000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>884000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>704000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>820000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>817000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>845000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>835000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>838000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>821000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>809000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>766000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>756000</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4295,110 +4388,113 @@
       <c r="AM43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1357000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1354000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1328000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1259000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1228000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1237000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1197000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1188000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>929000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>941000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>970000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1001000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1008000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>975000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>957000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>971000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>922000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>740000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>710000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>684000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>681000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>672000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>618000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>614000</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>671000</v>
       </c>
       <c r="AB44" s="3">
         <v>671000</v>
       </c>
       <c r="AC44" s="3">
+        <v>671000</v>
+      </c>
+      <c r="AD44" s="3">
         <v>729000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>722000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>701000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>628000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>603000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>523000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>481000</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4408,110 +4504,113 @@
       <c r="AM44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E45" s="3">
         <v>268000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>249000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>240000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>204000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>210000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>193000</v>
       </c>
       <c r="J45" s="3">
         <v>193000</v>
       </c>
       <c r="K45" s="3">
+        <v>193000</v>
+      </c>
+      <c r="L45" s="3">
         <v>192000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>173000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>266000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>174000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>189000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>199000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>198000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>186000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>165000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>146000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>179000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>198000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>156000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>173000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>161000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>163000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>164000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>175000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>134000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>147000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>111000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>95000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>72000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>74000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>65000</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4521,110 +4620,113 @@
       <c r="AM45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3174000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3358000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3072000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3392000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3061000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3172000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3037000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2884000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2677000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2743000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2615000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2622000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2495000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2502000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2450000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2481000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2339000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2541000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2507000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2356000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2220000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2225000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1923000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1843000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1993000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1785000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1840000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1846000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1862000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1809000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1668000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1456000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1377000</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4634,13 +4736,16 @@
       <c r="AM46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1000</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
         <v>1000</v>
@@ -4649,35 +4754,35 @@
         <v>1000</v>
       </c>
       <c r="G47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H47" s="3">
         <v>2000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>10000</v>
       </c>
       <c r="L47" s="3">
         <v>10000</v>
       </c>
       <c r="M47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N47" s="3">
         <v>18000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>17000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4747,110 +4852,113 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>759000</v>
+      </c>
+      <c r="E48" s="3">
         <v>774000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>764000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>695000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>652000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>658000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>648000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>658000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>552000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>582000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>577000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>580000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>571000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>557000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>538000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>535000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>514000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>428000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>424000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>438000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>442000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>451000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>445000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>440000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>433000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>453000</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>436000</v>
       </c>
       <c r="AD48" s="3">
         <v>436000</v>
       </c>
       <c r="AE48" s="3">
+        <v>436000</v>
+      </c>
+      <c r="AF48" s="3">
         <v>413000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>300000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>276000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>264000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>267000</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4860,110 +4968,113 @@
       <c r="AM48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4165000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4191000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4235000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4263000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4241000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4248000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4316000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4297000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3145000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3166000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3143000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3204000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3207000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3199000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3138000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3158000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3125000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2661000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2671000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2682000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2675000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2691000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2657000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2638000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2612000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2769000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2757000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2777000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2772000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2767000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2776000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2766000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2810000</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4973,8 +5084,11 @@
       <c r="AM49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5086,8 +5200,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5199,8 +5316,11 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5208,101 +5328,101 @@
         <v>109000</v>
       </c>
       <c r="E52" s="3">
+        <v>109000</v>
+      </c>
+      <c r="F52" s="3">
         <v>116000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>164000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>118000</v>
       </c>
       <c r="H52" s="3">
         <v>118000</v>
       </c>
       <c r="I52" s="3">
+        <v>118000</v>
+      </c>
+      <c r="J52" s="3">
         <v>132000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>137000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>136000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>144000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>106000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>110000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>109000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>129000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>136000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>142000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>267000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>223000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>232000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>236000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>239000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>243000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>244000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>245000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>249000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>121000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>100000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>101000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>97000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>96000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>22000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>21000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5312,8 +5432,11 @@
       <c r="AM52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5425,110 +5548,113 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8207000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8433000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8188000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8515000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8074000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8199000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8135000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7984000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6520000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6645000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6459000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6536000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6399000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6387000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6262000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6316000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6245000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5853000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5834000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5712000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5576000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5610000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5269000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5166000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5287000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5128000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5133000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5160000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5144000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4972000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4742000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4507000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>4482000</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5538,8 +5664,11 @@
       <c r="AM54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5579,8 +5708,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5620,110 +5750,111 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1015000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1131000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1037000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1102000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>971000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1073000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1021000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>980000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>858000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>905000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>863000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>948000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>894000</v>
       </c>
       <c r="P57" s="3">
         <v>894000</v>
       </c>
       <c r="Q57" s="3">
+        <v>894000</v>
+      </c>
+      <c r="R57" s="3">
         <v>936000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>987000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>958000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>883000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>905000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>915000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>908000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>936000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>858000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>811000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>906000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>920000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>932000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1009000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1013000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>964000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>850000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>774000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>712000</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5733,8 +5864,11 @@
       <c r="AM57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5742,40 +5876,40 @@
         <v>75000</v>
       </c>
       <c r="E58" s="3">
+        <v>75000</v>
+      </c>
+      <c r="F58" s="3">
         <v>82000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>66000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>59000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>57000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>56000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>64000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>50000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>51000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>48000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>50000</v>
       </c>
       <c r="O58" s="3">
         <v>50000</v>
       </c>
       <c r="P58" s="3">
-        <v>12000</v>
+        <v>50000</v>
       </c>
       <c r="Q58" s="3">
         <v>12000</v>
@@ -5787,7 +5921,7 @@
         <v>12000</v>
       </c>
       <c r="T58" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="U58" s="3">
         <v>10000</v>
@@ -5799,25 +5933,25 @@
         <v>10000</v>
       </c>
       <c r="X58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="Y58" s="3">
         <v>7000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>181000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>287000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>382000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>22000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>88000</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>22000</v>
       </c>
       <c r="AE58" s="3">
         <v>22000</v>
@@ -5825,8 +5959,8 @@
       <c r="AF58" s="3">
         <v>22000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
+      <c r="AG58" s="3">
+        <v>22000</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>8</v>
@@ -5846,110 +5980,113 @@
       <c r="AM58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
         <v>21000</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="E59" s="3">
+        <v>21000</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>1838000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>238000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>171000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>236000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>196000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>216000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>232000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>253000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>198000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>210000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>640000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>594000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>580000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>576000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>601000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>617000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>586000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>528000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>595000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>606000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>564000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>467000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>552000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>531000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>528000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>524000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>503000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>550000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>459000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>418000</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5959,110 +6096,113 @@
       <c r="AM59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1531000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1755000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1632000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3382000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1578000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1790000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1672000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1594000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1385000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1525000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1467000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1524000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1469000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1546000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1542000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1579000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1546000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1494000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1532000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1511000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1446000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1538000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1645000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1662000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1755000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1494000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1551000</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>1559000</v>
       </c>
       <c r="AE60" s="3">
         <v>1559000</v>
       </c>
       <c r="AF60" s="3">
+        <v>1559000</v>
+      </c>
+      <c r="AG60" s="3">
         <v>1489000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1400000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1233000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1130000</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK60" s="3" t="s">
         <v>8</v>
       </c>
@@ -6072,101 +6212,104 @@
       <c r="AM60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3441000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3456000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3464000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2215000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2190000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2195000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2177000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2181000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1553000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1562000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1571000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1566000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1568000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1404000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1407000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1410000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1412000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1220000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1222000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1184000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1186000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1155000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1006000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1011000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1149000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1158000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1165000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1169000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1174000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1179000</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -6185,110 +6328,113 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E62" s="3">
         <v>213000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>321000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>304000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>959000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>805000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>932000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>915000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>813000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>692000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>776000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>769000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>758000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>908000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>913000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>933000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>926000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>887000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>922000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>914000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>912000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>924000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1013000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>998000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>862000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>874000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>844000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>839000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>819000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>771000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>657000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>794000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>763000</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6298,8 +6444,11 @@
       <c r="AM62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6411,8 +6560,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6524,8 +6676,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6637,110 +6792,113 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5285000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5516000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5417000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5901000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4727000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4890000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4781000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4690000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3751000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3896000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3814000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3859000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3795000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3858000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3862000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3922000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3884000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3601000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3676000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3609000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3544000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3617000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3664000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3671000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3766000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3526000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3560000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3567000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3552000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3439000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2057000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2027000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1893000</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6750,8 +6908,11 @@
       <c r="AM66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6791,8 +6952,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6904,8 +7066,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7017,8 +7182,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7044,7 +7212,7 @@
         <v>482000</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>482000</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -7130,8 +7298,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7243,101 +7414,104 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E72" s="3">
         <v>345000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>218000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>71000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>904000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>907000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>893000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>881000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>853000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>810000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>728000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>707000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>657000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>600000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>561000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>498000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>404000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>317000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>250000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>182000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>124000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>75000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>16000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-59000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>38000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>47000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>39000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>50000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2000</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7356,8 +7530,11 @@
       <c r="AM72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7469,8 +7646,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7582,8 +7762,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7695,110 +7878,113 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2440000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2435000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2289000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2132000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2865000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2827000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2872000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2812000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2769000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2749000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2645000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2677000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2604000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2529000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2400000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2394000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2361000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2252000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2158000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2103000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2032000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1993000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1605000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1495000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1521000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1602000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1573000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1593000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1592000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1533000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2685000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2480000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2589000</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7808,8 +7994,11 @@
       <c r="AM76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7921,239 +8110,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44380</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44289</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E81" s="3">
         <v>136000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>156000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-825000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>23000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>43000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>82000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>50000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>57000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>39000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>63000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>94000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>87000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>67000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>68000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>58000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>49000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>59000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>75000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>48000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>16000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>311000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>33000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>45000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-449000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>23000</v>
-      </c>
-      <c r="AL81" s="3">
-        <v>16000</v>
       </c>
       <c r="AM81" s="3">
         <v>16000</v>
       </c>
+      <c r="AN81" s="3">
+        <v>16000</v>
+      </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8193,8 +8391,9 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8205,97 +8404,97 @@
         <v>17000</v>
       </c>
       <c r="F83" s="3">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="G83" s="3">
         <v>15000</v>
       </c>
       <c r="H83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I83" s="3">
         <v>17000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>15000</v>
       </c>
       <c r="M83" s="3">
         <v>15000</v>
       </c>
       <c r="N83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="O83" s="3">
         <v>9000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>25000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>20000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>21000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>22000</v>
       </c>
       <c r="V83" s="3">
         <v>22000</v>
       </c>
       <c r="W83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="X83" s="3">
         <v>23000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>22000</v>
       </c>
       <c r="Y83" s="3">
         <v>22000</v>
       </c>
       <c r="Z83" s="3">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="AA83" s="3">
         <v>21000</v>
       </c>
       <c r="AB83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AC83" s="3">
         <v>25000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>19000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>20000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>16000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>17000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>16000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>13000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>20000</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>17000</v>
       </c>
       <c r="AK83" s="3">
         <v>17000</v>
@@ -8304,10 +8503,13 @@
         <v>17000</v>
       </c>
       <c r="AM83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AN83" s="3">
         <v>16000</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8419,8 +8621,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8532,8 +8737,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8645,8 +8853,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8758,8 +8969,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8871,121 +9085,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-145000</v>
+      </c>
+      <c r="E89" s="3">
         <v>299000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1571000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>200000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-65000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>203000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>147000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>92000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>263000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>60000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>121000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>139000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>37000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>35000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-59000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>112000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>104000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>94000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>152000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>21000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>145000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-74000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>93000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-33000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-27000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>87000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>117000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>132000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>126000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-143000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>111000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>30000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9025,121 +9245,125 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-37000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-22000</v>
       </c>
       <c r="I91" s="3">
         <v>-22000</v>
       </c>
       <c r="J91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-15000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-31000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-29000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-51000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-19000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-23000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9251,8 +9475,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9364,121 +9591,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E94" s="3">
         <v>40000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-20000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1342000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>46000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-29000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-57000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-37000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-665000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-18000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-24000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-51000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-34000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-39000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-9000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9518,8 +9751,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9559,8 +9793,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9631,8 +9865,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9744,8 +9981,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9857,8 +10097,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9970,343 +10213,355 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-31000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1192000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-22000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1060000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-29000</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-9000</v>
       </c>
       <c r="O100" s="3">
         <v>-9000</v>
       </c>
       <c r="P100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>189000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-8000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>21000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>13000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>118000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-106000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-108000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>349000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-75000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>53000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-23000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>19000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>15000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-102000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>157000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-88000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-20000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-28000</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2000</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-25000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-13000</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5000</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>2000</v>
       </c>
       <c r="Z101" s="3">
         <v>2000</v>
       </c>
       <c r="AA101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AK101" s="3">
-        <v>2000</v>
       </c>
       <c r="AL101" s="3">
         <v>2000</v>
       </c>
       <c r="AM101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AN101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-222000</v>
+      </c>
+      <c r="E102" s="3">
         <v>316000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-408000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>176000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-115000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>161000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>118000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-190000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-33000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>267000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>87000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-33000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>74000</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>11000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-535000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>93000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>107000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>71000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>257000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-102000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>24000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>216000</v>
-      </c>
-      <c r="AB102" s="3">
-        <v>-10000</v>
       </c>
       <c r="AC102" s="3">
         <v>-10000</v>
       </c>
       <c r="AD102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>81000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>91000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>18000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>10000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>3000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-3000</v>
       </c>
     </row>
